--- a/Data to be imported for ticket system.xlsx
+++ b/Data to be imported for ticket system.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\Brandon Woods\McCracken Ticket System\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pstanam.MRX\Downloads\OneDrive_2026-02-23\McCraken Ticket System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31CB22A6-FB63-4E80-B93B-1F9FFCFE4FCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D91717D-355D-45D2-B263-23AECB6B05ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39120" yWindow="2520" windowWidth="28770" windowHeight="15450" activeTab="2" xr2:uid="{4459D843-6BF4-46C9-84A1-FE9E63F374D6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21120" activeTab="1" xr2:uid="{4459D843-6BF4-46C9-84A1-FE9E63F374D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Trucks" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="1087">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="1090">
   <si>
     <t>Truck Number</t>
   </si>
@@ -3323,6 +3323,15 @@
   </si>
   <si>
     <t>Brad Wynveen</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>OUT</t>
+  </si>
+  <si>
+    <t>Material new name</t>
   </si>
 </sst>
 </file>
@@ -3543,7 +3552,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3659,6 +3668,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -3687,7 +3705,6 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Report"/>
@@ -3704,10 +3721,10 @@
       <sheetName val="Price Sheet Proof"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1">
         <row r="75">
           <cell r="D75">
             <v>10</v>
@@ -4143,14 +4160,14 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -7660,14 +7677,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923037E0-AA5D-4E4D-AAE8-F525515C6536}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.42578125" customWidth="1"/>
     <col min="3" max="3" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>382</v>
       </c>
@@ -7701,17 +7718,23 @@
       <c r="K1" s="23" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" s="53" t="s">
+        <v>1087</v>
+      </c>
+      <c r="M1" s="53" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="24">
-        <f t="shared" ref="A2:A31" si="0">VLOOKUP(B2,CatLU,3,FALSE)</f>
+        <f t="shared" ref="A2:A26" si="0">VLOOKUP(B2,CatLU,3,FALSE)</f>
         <v>8</v>
       </c>
       <c r="B2" s="25" t="s">
         <v>393</v>
       </c>
       <c r="C2" s="26" t="str">
-        <f t="shared" ref="C2:C31" si="1">VLOOKUP(B2,Material,2,FALSE)</f>
+        <f>VLOOKUP(B2,Material,2,FALSE)</f>
         <v>Broken Asphalt (IN)</v>
       </c>
       <c r="D2" s="27">
@@ -7738,8 +7761,15 @@
       <c r="K2" s="27" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L2" s="54" t="s">
+        <v>821</v>
+      </c>
+      <c r="M2" t="str">
+        <f>IFERROR(TRIM(LEFT(C2,SEARCH("(",C2)-1)),C2)</f>
+        <v>Broken Asphalt</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -7748,7 +7778,7 @@
         <v>395</v>
       </c>
       <c r="C3" s="26" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="C2:C26" si="1">VLOOKUP(B3,Material,2,FALSE)</f>
         <v>Other Clean Hard Fill (IN)</v>
       </c>
       <c r="D3" s="27">
@@ -7775,8 +7805,15 @@
       <c r="K3" s="27" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3" s="54" t="s">
+        <v>821</v>
+      </c>
+      <c r="M3" t="str">
+        <f t="shared" ref="M3:M31" si="2">IFERROR(TRIM(LEFT(C3,SEARCH("(",C3)-1)),C3)</f>
+        <v>Other Clean Hard Fill</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="24">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -7812,8 +7849,15 @@
       <c r="K4" s="27" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4" s="54" t="s">
+        <v>821</v>
+      </c>
+      <c r="M4" t="str">
+        <f t="shared" si="2"/>
+        <v>Broken Concrete</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="24">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -7849,8 +7893,15 @@
       <c r="K5" s="27" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5" s="54" t="s">
+        <v>821</v>
+      </c>
+      <c r="M5" t="str">
+        <f t="shared" si="2"/>
+        <v>Bulk Topsoil</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="24">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -7886,8 +7937,15 @@
       <c r="K6" s="27" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L6" s="54" t="s">
+        <v>821</v>
+      </c>
+      <c r="M6" t="str">
+        <f t="shared" si="2"/>
+        <v>Bridge Deck</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -7923,8 +7981,15 @@
       <c r="K7" s="27">
         <v>225</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L7" s="54" t="s">
+        <v>821</v>
+      </c>
+      <c r="M7" t="str">
+        <f t="shared" si="2"/>
+        <v>Other Clean Hard Fill</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="24">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -7960,8 +8025,15 @@
       <c r="K8" s="27" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L8" s="54" t="s">
+        <v>821</v>
+      </c>
+      <c r="M8" t="str">
+        <f t="shared" si="2"/>
+        <v>Asphalt Grindings</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -7997,8 +8069,15 @@
       <c r="K9" s="27" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L9" s="54" t="s">
+        <v>821</v>
+      </c>
+      <c r="M9" t="str">
+        <f t="shared" si="2"/>
+        <v>Other Clean Hard Fill</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="24">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -8034,8 +8113,15 @@
       <c r="K10" s="27" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L10" s="54" t="s">
+        <v>821</v>
+      </c>
+      <c r="M10" t="str">
+        <f t="shared" si="2"/>
+        <v>Sand</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -8071,8 +8157,15 @@
       <c r="K11" s="27" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L11" s="54" t="s">
+        <v>821</v>
+      </c>
+      <c r="M11" t="str">
+        <f t="shared" si="2"/>
+        <v>Rubble</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="24">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -8108,8 +8201,15 @@
       <c r="K12" s="27" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L12" s="54" t="s">
+        <v>821</v>
+      </c>
+      <c r="M12" t="str">
+        <f t="shared" si="2"/>
+        <v>Slop</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -8118,7 +8218,7 @@
         <v>405</v>
       </c>
       <c r="C13" s="26" t="str">
-        <f t="shared" si="1"/>
+        <f>VLOOKUP(B13,Material,2,FALSE)</f>
         <v>Other Clean Hard Fill (IN)</v>
       </c>
       <c r="D13" s="27">
@@ -8145,8 +8245,15 @@
       <c r="K13" s="27" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L13" s="54" t="s">
+        <v>821</v>
+      </c>
+      <c r="M13" t="str">
+        <f t="shared" si="2"/>
+        <v>Other Clean Hard Fill</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="24">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -8182,8 +8289,15 @@
       <c r="K14" s="27" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L14" s="54" t="s">
+        <v>821</v>
+      </c>
+      <c r="M14" t="str">
+        <f t="shared" si="2"/>
+        <v>Compactable Fill Dirt</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="24">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -8219,8 +8333,15 @@
       <c r="K15" s="27" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L15" s="54" t="s">
+        <v>821</v>
+      </c>
+      <c r="M15" t="str">
+        <f t="shared" si="2"/>
+        <v>Certified</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="24">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -8256,8 +8377,15 @@
       <c r="K16" s="27" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L16" s="54" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M16" t="str">
+        <f t="shared" si="2"/>
+        <v>Bulk Sand</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="24">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -8293,8 +8421,15 @@
       <c r="K17" s="27" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L17" s="54" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M17" t="str">
+        <f t="shared" si="2"/>
+        <v>Sand Screened</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="24">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -8330,8 +8465,15 @@
       <c r="K18" s="27" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L18" s="54" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M18" t="str">
+        <f t="shared" si="2"/>
+        <v>Fill Dirt</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="24">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -8367,8 +8509,15 @@
       <c r="K19" s="27" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L19" s="54" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M19" t="str">
+        <f t="shared" si="2"/>
+        <v>Asphalt Grindings</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="24">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -8404,8 +8553,15 @@
       <c r="K20" s="27" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L20" s="54" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M20" t="str">
+        <f t="shared" si="2"/>
+        <v>Bulk Topsoil</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="24">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -8441,8 +8597,15 @@
       <c r="K21" s="27" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L21" s="54" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M21" t="str">
+        <f t="shared" si="2"/>
+        <v>Screened Topsoil</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="24">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -8478,8 +8641,15 @@
       <c r="K22" s="27" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L22" s="55" t="s">
+        <v>821</v>
+      </c>
+      <c r="M22" t="str">
+        <f t="shared" si="2"/>
+        <v>Yard - Grass,Leaves,Woodchips</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="24">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -8515,8 +8685,15 @@
       <c r="K23" s="27" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L23" s="55" t="s">
+        <v>821</v>
+      </c>
+      <c r="M23" t="str">
+        <f t="shared" si="2"/>
+        <v>Tree Stumps</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="24">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -8552,8 +8729,15 @@
       <c r="K24" s="27" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L24" s="54" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M24" t="str">
+        <f t="shared" si="2"/>
+        <v>#304 Limestone</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="24">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -8589,8 +8773,15 @@
       <c r="K25" s="27" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L25" s="54" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M25" t="str">
+        <f t="shared" si="2"/>
+        <v>#57 Limestone</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="24">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -8626,8 +8817,15 @@
       <c r="K26" s="30" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L26" s="54" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M26" t="str">
+        <f t="shared" si="2"/>
+        <v>#10 Limestone</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="24">
         <f>VLOOKUP(B27,CatLU,3,FALSE)</f>
         <v>40</v>
@@ -8663,8 +8861,15 @@
       <c r="K27" s="32" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L27" s="54" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M27" t="str">
+        <f t="shared" si="2"/>
+        <v>#304 Recycled Concrete</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="24">
         <f>VLOOKUP(B28,CatLU,3,FALSE)</f>
         <v>41</v>
@@ -8700,8 +8905,15 @@
       <c r="K28" s="32" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L28" s="54" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M28" t="str">
+        <f t="shared" si="2"/>
+        <v>#1&amp;2 Recycled Concrete</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="24">
         <f>VLOOKUP(B29,CatLU,3,FALSE)</f>
         <v>42</v>
@@ -8737,8 +8949,15 @@
       <c r="K29" s="32" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L29" s="54" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M29" t="str">
+        <f t="shared" si="2"/>
+        <v>#57 Recycled Concrete</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="24">
         <f>VLOOKUP(B30,CatLU,3,FALSE)</f>
         <v>80</v>
@@ -8774,8 +8993,15 @@
       <c r="K30" s="32" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L30" s="54" t="s">
+        <v>821</v>
+      </c>
+      <c r="M30" t="str">
+        <f t="shared" si="2"/>
+        <v>Snow In</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="24">
         <v>14</v>
       </c>
@@ -8809,6 +9035,22 @@
       <c r="K31" s="32" t="s">
         <v>394</v>
       </c>
+      <c r="L31" s="54" t="s">
+        <v>821</v>
+      </c>
+      <c r="M31" t="str">
+        <f t="shared" si="2"/>
+        <v>Wet Dirt w/ Organics</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L32" s="54"/>
+    </row>
+    <row r="33" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L33" s="54"/>
+    </row>
+    <row r="34" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L34" s="54"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data to be imported for ticket system.xlsx
+++ b/Data to be imported for ticket system.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pstanam.MRX\Downloads\OneDrive_2026-02-23\McCraken Ticket System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D91717D-355D-45D2-B263-23AECB6B05ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD1D7EE-BDD8-48B3-97EA-68849BD14E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21120" activeTab="1" xr2:uid="{4459D843-6BF4-46C9-84A1-FE9E63F374D6}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{4459D843-6BF4-46C9-84A1-FE9E63F374D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Trucks" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="1090">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="1087">
   <si>
     <t>Truck Number</t>
   </si>
@@ -1249,9 +1249,6 @@
     <t>NA</t>
   </si>
   <si>
-    <t>Bric</t>
-  </si>
-  <si>
     <t>Conc</t>
   </si>
   <si>
@@ -1267,9 +1264,6 @@
     <t>Grin</t>
   </si>
   <si>
-    <t>Rtop</t>
-  </si>
-  <si>
     <t>Sand</t>
   </si>
   <si>
@@ -1277,9 +1271,6 @@
   </si>
   <si>
     <t>Slop</t>
-  </si>
-  <si>
-    <t>OCHF</t>
   </si>
   <si>
     <t>Comp</t>
@@ -3552,7 +3543,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3668,14 +3659,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -7677,7 +7674,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923037E0-AA5D-4E4D-AAE8-F525515C6536}">
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.42578125" customWidth="1"/>
@@ -7719,129 +7716,129 @@
         <v>392</v>
       </c>
       <c r="L1" s="53" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="M1" s="53" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="24">
-        <f t="shared" ref="A2:A26" si="0">VLOOKUP(B2,CatLU,3,FALSE)</f>
-        <v>8</v>
-      </c>
-      <c r="B2" s="25" t="s">
-        <v>393</v>
+        <f>VLOOKUP(B2,CatLU,3,FALSE)</f>
+        <v>41</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>414</v>
       </c>
       <c r="C2" s="26" t="str">
         <f>VLOOKUP(B2,Material,2,FALSE)</f>
-        <v>Broken Asphalt (IN)</v>
-      </c>
-      <c r="D2" s="27">
-        <v>125</v>
-      </c>
-      <c r="E2" s="27">
-        <v>150</v>
-      </c>
-      <c r="F2" s="27">
-        <v>200</v>
-      </c>
-      <c r="G2" s="27">
-        <v>275</v>
-      </c>
-      <c r="H2" s="27">
-        <v>300</v>
-      </c>
-      <c r="I2" s="27">
-        <v>325</v>
-      </c>
-      <c r="J2" s="27" t="s">
+        <v>#1&amp;2 Recycled Concrete (Out)</v>
+      </c>
+      <c r="D2" s="30">
+        <v>140</v>
+      </c>
+      <c r="E2" s="30">
+        <v>168</v>
+      </c>
+      <c r="F2" s="30">
+        <v>224</v>
+      </c>
+      <c r="G2" s="30">
+        <v>308</v>
+      </c>
+      <c r="H2" s="30">
+        <v>336</v>
+      </c>
+      <c r="I2" s="30">
+        <v>364</v>
+      </c>
+      <c r="J2" s="30" t="s">
         <v>394</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="K2" s="30" t="s">
         <v>394</v>
       </c>
       <c r="L2" s="54" t="s">
-        <v>821</v>
+        <v>1085</v>
       </c>
       <c r="M2" t="str">
         <f>IFERROR(TRIM(LEFT(C2,SEARCH("(",C2)-1)),C2)</f>
-        <v>Broken Asphalt</v>
+        <v>#1&amp;2 Recycled Concrete</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="24">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>395</v>
+        <f>VLOOKUP(B3,CatLU,3,FALSE)</f>
+        <v>33</v>
+      </c>
+      <c r="B3" s="29">
+        <v>10</v>
       </c>
       <c r="C3" s="26" t="str">
-        <f t="shared" ref="C2:C26" si="1">VLOOKUP(B3,Material,2,FALSE)</f>
-        <v>Other Clean Hard Fill (IN)</v>
-      </c>
-      <c r="D3" s="27">
-        <v>75</v>
-      </c>
-      <c r="E3" s="27">
-        <v>90</v>
-      </c>
-      <c r="F3" s="27">
-        <v>120</v>
-      </c>
-      <c r="G3" s="27">
-        <v>165</v>
-      </c>
-      <c r="H3" s="27">
-        <v>180</v>
-      </c>
-      <c r="I3" s="27">
-        <v>195</v>
-      </c>
-      <c r="J3" s="27" t="s">
+        <f>VLOOKUP(B3,Material,2,FALSE)</f>
+        <v>#10 Limestone (Out)</v>
+      </c>
+      <c r="D3" s="30">
+        <v>350</v>
+      </c>
+      <c r="E3" s="30">
+        <v>420</v>
+      </c>
+      <c r="F3" s="30">
+        <v>560</v>
+      </c>
+      <c r="G3" s="30">
+        <v>770</v>
+      </c>
+      <c r="H3" s="30">
+        <v>840</v>
+      </c>
+      <c r="I3" s="30">
+        <v>910</v>
+      </c>
+      <c r="J3" s="30" t="s">
         <v>394</v>
       </c>
-      <c r="K3" s="27" t="s">
+      <c r="K3" s="30" t="s">
         <v>394</v>
       </c>
       <c r="L3" s="54" t="s">
-        <v>821</v>
+        <v>1085</v>
       </c>
       <c r="M3" t="str">
-        <f t="shared" ref="M3:M31" si="2">IFERROR(TRIM(LEFT(C3,SEARCH("(",C3)-1)),C3)</f>
-        <v>Other Clean Hard Fill</v>
+        <f>IFERROR(TRIM(LEFT(C3,SEARCH("(",C3)-1)),C3)</f>
+        <v>#10 Limestone</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="24">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>396</v>
+        <f>VLOOKUP(B4,CatLU,3,FALSE)</f>
+        <v>32</v>
+      </c>
+      <c r="B4" s="25">
+        <v>304</v>
       </c>
       <c r="C4" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">Broken Concrete (IN) </v>
+        <f>VLOOKUP(B4,Material,2,FALSE)</f>
+        <v>#304 Limestone (Out)</v>
       </c>
       <c r="D4" s="27">
-        <v>75</v>
+        <v>350</v>
       </c>
       <c r="E4" s="27">
-        <v>90</v>
+        <v>420</v>
       </c>
       <c r="F4" s="27">
-        <v>120</v>
+        <v>560</v>
       </c>
       <c r="G4" s="27">
-        <v>165</v>
+        <v>770</v>
       </c>
       <c r="H4" s="27">
-        <v>180</v>
+        <v>840</v>
       </c>
       <c r="I4" s="27">
-        <v>195</v>
+        <v>910</v>
       </c>
       <c r="J4" s="27" t="s">
         <v>394</v>
@@ -7850,86 +7847,86 @@
         <v>394</v>
       </c>
       <c r="L4" s="54" t="s">
-        <v>821</v>
+        <v>1085</v>
       </c>
       <c r="M4" t="str">
-        <f t="shared" si="2"/>
-        <v>Broken Concrete</v>
+        <f>IFERROR(TRIM(LEFT(C4,SEARCH("(",C4)-1)),C4)</f>
+        <v>#304 Limestone</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="24">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>397</v>
+        <f>VLOOKUP(B5,CatLU,3,FALSE)</f>
+        <v>40</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>413</v>
       </c>
       <c r="C5" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>Bulk Topsoil (clean) (IN)</v>
-      </c>
-      <c r="D5" s="27">
-        <v>40</v>
-      </c>
-      <c r="E5" s="27">
-        <v>48</v>
-      </c>
-      <c r="F5" s="27">
-        <v>64</v>
-      </c>
-      <c r="G5" s="27">
-        <v>88</v>
-      </c>
-      <c r="H5" s="27">
-        <v>96</v>
-      </c>
-      <c r="I5" s="27">
-        <v>104</v>
-      </c>
-      <c r="J5" s="27" t="s">
+        <f>VLOOKUP(B5,Material,2,FALSE)</f>
+        <v>#304 Recycled Concrete (Out)</v>
+      </c>
+      <c r="D5" s="30">
+        <v>125</v>
+      </c>
+      <c r="E5" s="30">
+        <v>150</v>
+      </c>
+      <c r="F5" s="30">
+        <v>200</v>
+      </c>
+      <c r="G5" s="30">
+        <v>275</v>
+      </c>
+      <c r="H5" s="30">
+        <v>300</v>
+      </c>
+      <c r="I5" s="30">
+        <v>325</v>
+      </c>
+      <c r="J5" s="30" t="s">
         <v>394</v>
       </c>
-      <c r="K5" s="27" t="s">
+      <c r="K5" s="30" t="s">
         <v>394</v>
       </c>
       <c r="L5" s="54" t="s">
-        <v>821</v>
+        <v>1085</v>
       </c>
       <c r="M5" t="str">
-        <f t="shared" si="2"/>
-        <v>Bulk Topsoil</v>
+        <f>IFERROR(TRIM(LEFT(C5,SEARCH("(",C5)-1)),C5)</f>
+        <v>#304 Recycled Concrete</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="24">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>398</v>
+        <f>VLOOKUP(B6,CatLU,3,FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="B6" s="25">
+        <v>57</v>
       </c>
       <c r="C6" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>Bridge Deck (IN)</v>
+        <f>VLOOKUP(B6,Material,2,FALSE)</f>
+        <v>#57 Limestone (Out)</v>
       </c>
       <c r="D6" s="27">
-        <v>625</v>
+        <v>400</v>
       </c>
       <c r="E6" s="27">
-        <v>750</v>
+        <v>480</v>
       </c>
       <c r="F6" s="27">
-        <v>1000</v>
+        <v>640</v>
       </c>
       <c r="G6" s="27">
-        <v>1375</v>
+        <v>880</v>
       </c>
       <c r="H6" s="27">
-        <v>1500</v>
+        <v>960</v>
       </c>
       <c r="I6" s="27">
-        <v>1625</v>
+        <v>1040</v>
       </c>
       <c r="J6" s="27" t="s">
         <v>394</v>
@@ -7938,67 +7935,67 @@
         <v>394</v>
       </c>
       <c r="L6" s="54" t="s">
-        <v>821</v>
+        <v>1085</v>
       </c>
       <c r="M6" t="str">
-        <f t="shared" si="2"/>
-        <v>Bridge Deck</v>
+        <f>IFERROR(TRIM(LEFT(C6,SEARCH("(",C6)-1)),C6)</f>
+        <v>#57 Limestone</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="24">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>399</v>
+        <f>VLOOKUP(B7,CatLU,3,FALSE)</f>
+        <v>42</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>415</v>
       </c>
       <c r="C7" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>Other Clean Hard Fill (IN)</v>
-      </c>
-      <c r="D7" s="27">
-        <v>75</v>
-      </c>
-      <c r="E7" s="27">
-        <v>90</v>
-      </c>
-      <c r="F7" s="27">
-        <v>120</v>
-      </c>
-      <c r="G7" s="27">
-        <v>165</v>
-      </c>
-      <c r="H7" s="27">
+        <f>VLOOKUP(B7,Material,2,FALSE)</f>
+        <v>#57 Recycled Concrete (Out)</v>
+      </c>
+      <c r="D7" s="30">
+        <v>150</v>
+      </c>
+      <c r="E7" s="30">
         <v>180</v>
       </c>
-      <c r="I7" s="27">
-        <v>195</v>
-      </c>
-      <c r="J7" s="27" t="s">
+      <c r="F7" s="30">
+        <v>240</v>
+      </c>
+      <c r="G7" s="30">
+        <v>330</v>
+      </c>
+      <c r="H7" s="30">
+        <v>360</v>
+      </c>
+      <c r="I7" s="30">
+        <v>390</v>
+      </c>
+      <c r="J7" s="30" t="s">
         <v>394</v>
       </c>
-      <c r="K7" s="27">
-        <v>225</v>
+      <c r="K7" s="30" t="s">
+        <v>394</v>
       </c>
       <c r="L7" s="54" t="s">
-        <v>821</v>
+        <v>1085</v>
       </c>
       <c r="M7" t="str">
-        <f t="shared" si="2"/>
-        <v>Other Clean Hard Fill</v>
+        <f>IFERROR(TRIM(LEFT(C7,SEARCH("(",C7)-1)),C7)</f>
+        <v>#57 Recycled Concrete</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="24">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP(B8,CatLU,3,FALSE)</f>
         <v>1</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C8" s="26" t="str">
-        <f t="shared" si="1"/>
+        <f>VLOOKUP(B8,Material,2,FALSE)</f>
         <v>Asphalt Grindings (no chunks) (IN)</v>
       </c>
       <c r="D8" s="27">
@@ -8026,42 +8023,42 @@
         <v>394</v>
       </c>
       <c r="L8" s="54" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="M8" t="str">
-        <f t="shared" si="2"/>
+        <f>IFERROR(TRIM(LEFT(C8,SEARCH("(",C8)-1)),C8)</f>
         <v>Asphalt Grindings</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="24">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>VLOOKUP(B9,CatLU,3,FALSE)</f>
+        <v>22</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="C9" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>Other Clean Hard Fill (IN)</v>
+        <f>VLOOKUP(B9,Material,2,FALSE)</f>
+        <v>Asphalt Grindings (OUT)</v>
       </c>
       <c r="D9" s="27">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E9" s="27">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F9" s="27">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G9" s="27">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="H9" s="27">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="I9" s="27">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="J9" s="27" t="s">
         <v>394</v>
@@ -8070,42 +8067,42 @@
         <v>394</v>
       </c>
       <c r="L9" s="54" t="s">
-        <v>821</v>
+        <v>1085</v>
       </c>
       <c r="M9" t="str">
-        <f t="shared" si="2"/>
-        <v>Other Clean Hard Fill</v>
+        <f>IFERROR(TRIM(LEFT(C9,SEARCH("(",C9)-1)),C9)</f>
+        <v>Asphalt Grindings</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="24">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>VLOOKUP(B10,CatLU,3,FALSE)</f>
+        <v>12</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C10" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>Sand (pre-screened) (IN)</v>
+        <f>VLOOKUP(B10,Material,2,FALSE)</f>
+        <v>Bridge Deck (IN)</v>
       </c>
       <c r="D10" s="27">
-        <v>30</v>
+        <v>625</v>
       </c>
       <c r="E10" s="27">
-        <v>36</v>
+        <v>750</v>
       </c>
       <c r="F10" s="27">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="G10" s="27">
-        <v>66</v>
+        <v>1375</v>
       </c>
       <c r="H10" s="27">
-        <v>72</v>
+        <v>1500</v>
       </c>
       <c r="I10" s="27">
-        <v>78</v>
+        <v>1625</v>
       </c>
       <c r="J10" s="27" t="s">
         <v>394</v>
@@ -8114,42 +8111,42 @@
         <v>394</v>
       </c>
       <c r="L10" s="54" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="M10" t="str">
-        <f t="shared" si="2"/>
-        <v>Sand</v>
+        <f>IFERROR(TRIM(LEFT(C10,SEARCH("(",C10)-1)),C10)</f>
+        <v>Bridge Deck</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="24">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>VLOOKUP(B11,CatLU,3,FALSE)</f>
+        <v>8</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="C11" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>Rubble (In)</v>
+        <f>VLOOKUP(B11,Material,2,FALSE)</f>
+        <v>Broken Asphalt (IN)</v>
       </c>
       <c r="D11" s="27">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="E11" s="27">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="F11" s="27">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="G11" s="27">
-        <v>165</v>
+        <v>275</v>
       </c>
       <c r="H11" s="27">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="I11" s="27">
-        <v>195</v>
+        <v>325</v>
       </c>
       <c r="J11" s="27" t="s">
         <v>394</v>
@@ -8158,86 +8155,86 @@
         <v>394</v>
       </c>
       <c r="L11" s="54" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="M11" t="str">
-        <f t="shared" si="2"/>
-        <v>Rubble</v>
+        <f>IFERROR(TRIM(LEFT(C11,SEARCH("(",C11)-1)),C11)</f>
+        <v>Broken Asphalt</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="24">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <f>VLOOKUP(B12,CatLU,3,FALSE)</f>
+        <v>4</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="C12" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>Slop (IN)</v>
+        <f>VLOOKUP(B12,Material,2,FALSE)</f>
+        <v xml:space="preserve">Broken Concrete (IN) </v>
       </c>
       <c r="D12" s="27">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="E12" s="27">
-        <v>600</v>
+        <v>90</v>
       </c>
       <c r="F12" s="27">
-        <v>800</v>
+        <v>120</v>
       </c>
       <c r="G12" s="27">
-        <v>1100</v>
+        <v>165</v>
       </c>
       <c r="H12" s="27">
-        <v>1200</v>
+        <v>180</v>
       </c>
       <c r="I12" s="27">
-        <v>1300</v>
-      </c>
-      <c r="J12" s="27">
-        <v>500</v>
+        <v>195</v>
+      </c>
+      <c r="J12" s="27" t="s">
+        <v>394</v>
       </c>
       <c r="K12" s="27" t="s">
         <v>394</v>
       </c>
       <c r="L12" s="54" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="M12" t="str">
-        <f t="shared" si="2"/>
-        <v>Slop</v>
+        <f>IFERROR(TRIM(LEFT(C12,SEARCH("(",C12)-1)),C12)</f>
+        <v>Broken Concrete</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="24">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B13" s="28" t="s">
+        <f>VLOOKUP(B13,CatLU,3,FALSE)</f>
+        <v>20</v>
+      </c>
+      <c r="B13" s="25" t="s">
         <v>405</v>
       </c>
       <c r="C13" s="26" t="str">
         <f>VLOOKUP(B13,Material,2,FALSE)</f>
-        <v>Other Clean Hard Fill (IN)</v>
+        <v>Bulk Sand (PreScreened) (OUT)</v>
       </c>
       <c r="D13" s="27">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E13" s="27">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F13" s="27">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="G13" s="27">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="H13" s="27">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="I13" s="27">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="J13" s="27" t="s">
         <v>394</v>
@@ -8246,42 +8243,42 @@
         <v>394</v>
       </c>
       <c r="L13" s="54" t="s">
-        <v>821</v>
+        <v>1085</v>
       </c>
       <c r="M13" t="str">
-        <f t="shared" si="2"/>
-        <v>Other Clean Hard Fill</v>
+        <f>IFERROR(TRIM(LEFT(C13,SEARCH("(",C13)-1)),C13)</f>
+        <v>Bulk Sand</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="24">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="B14" s="28" t="s">
-        <v>406</v>
+        <f>VLOOKUP(B14,CatLU,3,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>396</v>
       </c>
       <c r="C14" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>Compactable Fill Dirt (IN)</v>
+        <f>VLOOKUP(B14,Material,2,FALSE)</f>
+        <v>Bulk Topsoil (clean) (IN)</v>
       </c>
       <c r="D14" s="27">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E14" s="27">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F14" s="27">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="G14" s="27">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="H14" s="27">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="I14" s="27">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="J14" s="27" t="s">
         <v>394</v>
@@ -8290,42 +8287,42 @@
         <v>394</v>
       </c>
       <c r="L14" s="54" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="M14" t="str">
-        <f t="shared" si="2"/>
-        <v>Compactable Fill Dirt</v>
+        <f>IFERROR(TRIM(LEFT(C14,SEARCH("(",C14)-1)),C14)</f>
+        <v>Bulk Topsoil</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="24">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B15" s="28" t="s">
-        <v>407</v>
+        <f>VLOOKUP(B15,CatLU,3,FALSE)</f>
+        <v>23</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>409</v>
       </c>
       <c r="C15" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">Certified (IN) </v>
+        <f>VLOOKUP(B15,Material,2,FALSE)</f>
+        <v>Bulk Topsoil (OUT)</v>
       </c>
       <c r="D15" s="27">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E15" s="27">
+        <v>48</v>
+      </c>
+      <c r="F15" s="27">
+        <v>64</v>
+      </c>
+      <c r="G15" s="27">
+        <v>88</v>
+      </c>
+      <c r="H15" s="27">
         <v>96</v>
       </c>
-      <c r="F15" s="27">
-        <v>128</v>
-      </c>
-      <c r="G15" s="27">
-        <v>176</v>
-      </c>
-      <c r="H15" s="27">
-        <v>192</v>
-      </c>
       <c r="I15" s="27">
-        <v>208</v>
+        <v>104</v>
       </c>
       <c r="J15" s="27" t="s">
         <v>394</v>
@@ -8334,42 +8331,42 @@
         <v>394</v>
       </c>
       <c r="L15" s="54" t="s">
-        <v>821</v>
+        <v>1085</v>
       </c>
       <c r="M15" t="str">
-        <f t="shared" si="2"/>
-        <v>Certified</v>
+        <f>IFERROR(TRIM(LEFT(C15,SEARCH("(",C15)-1)),C15)</f>
+        <v>Bulk Topsoil</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="24">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>408</v>
+        <f>VLOOKUP(B16,CatLU,3,FALSE)</f>
+        <v>7</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>404</v>
       </c>
       <c r="C16" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>Bulk Sand (PreScreened) (OUT)</v>
+        <f>VLOOKUP(B16,Material,2,FALSE)</f>
+        <v xml:space="preserve">Certified (IN) </v>
       </c>
       <c r="D16" s="27">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E16" s="27">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="F16" s="27">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="G16" s="27">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="H16" s="27">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="I16" s="27">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="J16" s="27" t="s">
         <v>394</v>
@@ -8378,42 +8375,42 @@
         <v>394</v>
       </c>
       <c r="L16" s="54" t="s">
-        <v>1088</v>
+        <v>818</v>
       </c>
       <c r="M16" t="str">
-        <f t="shared" si="2"/>
-        <v>Bulk Sand</v>
+        <f>IFERROR(TRIM(LEFT(C16,SEARCH("(",C16)-1)),C16)</f>
+        <v>Certified</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="24">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP(B17,CatLU,3,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>403</v>
+      </c>
+      <c r="C17" s="26" t="str">
+        <f>VLOOKUP(B17,Material,2,FALSE)</f>
+        <v>Compactable Fill Dirt (IN)</v>
+      </c>
+      <c r="D17" s="27">
         <v>30</v>
       </c>
-      <c r="B17" s="25" t="s">
-        <v>409</v>
-      </c>
-      <c r="C17" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>Sand Screened (OUT)</v>
-      </c>
-      <c r="D17" s="27">
-        <v>90</v>
-      </c>
       <c r="E17" s="27">
-        <v>108</v>
+        <v>36</v>
       </c>
       <c r="F17" s="27">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="G17" s="27">
-        <v>198</v>
+        <v>66</v>
       </c>
       <c r="H17" s="27">
-        <v>216</v>
+        <v>72</v>
       </c>
       <c r="I17" s="27">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="J17" s="27" t="s">
         <v>394</v>
@@ -8422,23 +8419,23 @@
         <v>394</v>
       </c>
       <c r="L17" s="54" t="s">
-        <v>1088</v>
+        <v>818</v>
       </c>
       <c r="M17" t="str">
-        <f t="shared" si="2"/>
-        <v>Sand Screened</v>
+        <f>IFERROR(TRIM(LEFT(C17,SEARCH("(",C17)-1)),C17)</f>
+        <v>Compactable Fill Dirt</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="24">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP(B18,CatLU,3,FALSE)</f>
         <v>21</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C18" s="26" t="str">
-        <f t="shared" si="1"/>
+        <f>VLOOKUP(B18,Material,2,FALSE)</f>
         <v>Fill Dirt (OUT)</v>
       </c>
       <c r="D18" s="27">
@@ -8466,86 +8463,86 @@
         <v>394</v>
       </c>
       <c r="L18" s="54" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="M18" t="str">
-        <f t="shared" si="2"/>
+        <f>IFERROR(TRIM(LEFT(C18,SEARCH("(",C18)-1)),C18)</f>
         <v>Fill Dirt</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="24">
-        <f t="shared" si="0"/>
-        <v>22</v>
+        <f>VLOOKUP(B19,CatLU,3,FALSE)</f>
+        <v>5</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="C19" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>Asphalt Grindings (OUT)</v>
+        <f>VLOOKUP(B19,Material,2,FALSE)</f>
+        <v>Other Clean Hard Fill (IN)</v>
       </c>
       <c r="D19" s="27">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E19" s="27">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="F19" s="27">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G19" s="27">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="H19" s="27">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="I19" s="27">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="J19" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="K19" s="27" t="s">
-        <v>394</v>
+      <c r="K19" s="27">
+        <v>225</v>
       </c>
       <c r="L19" s="54" t="s">
-        <v>1088</v>
+        <v>818</v>
       </c>
       <c r="M19" t="str">
-        <f t="shared" si="2"/>
-        <v>Asphalt Grindings</v>
+        <f>IFERROR(TRIM(LEFT(C19,SEARCH("(",C19)-1)),C19)</f>
+        <v>Other Clean Hard Fill</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="24">
-        <f t="shared" si="0"/>
-        <v>23</v>
+        <f>VLOOKUP(B20,CatLU,3,FALSE)</f>
+        <v>5</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="C20" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>Bulk Topsoil (OUT)</v>
+        <f>VLOOKUP(B20,Material,2,FALSE)</f>
+        <v>Rubble (In)</v>
       </c>
       <c r="D20" s="27">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="E20" s="27">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="F20" s="27">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="G20" s="27">
-        <v>88</v>
+        <v>165</v>
       </c>
       <c r="H20" s="27">
-        <v>96</v>
+        <v>180</v>
       </c>
       <c r="I20" s="27">
-        <v>104</v>
+        <v>195</v>
       </c>
       <c r="J20" s="27" t="s">
         <v>394</v>
@@ -8554,42 +8551,42 @@
         <v>394</v>
       </c>
       <c r="L20" s="54" t="s">
-        <v>1088</v>
+        <v>818</v>
       </c>
       <c r="M20" t="str">
-        <f t="shared" si="2"/>
-        <v>Bulk Topsoil</v>
+        <f>IFERROR(TRIM(LEFT(C20,SEARCH("(",C20)-1)),C20)</f>
+        <v>Rubble</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="24">
-        <f t="shared" si="0"/>
-        <v>31</v>
+        <f>VLOOKUP(B21,CatLU,3,FALSE)</f>
+        <v>2</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="C21" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>Screened Topsoil (OUT)</v>
+        <f>VLOOKUP(B21,Material,2,FALSE)</f>
+        <v>Sand (pre-screened) (IN)</v>
       </c>
       <c r="D21" s="27">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="E21" s="27">
-        <v>180</v>
+        <v>36</v>
       </c>
       <c r="F21" s="27">
-        <v>240</v>
+        <v>48</v>
       </c>
       <c r="G21" s="27">
-        <v>330</v>
+        <v>66</v>
       </c>
       <c r="H21" s="27">
-        <v>360</v>
+        <v>72</v>
       </c>
       <c r="I21" s="27">
-        <v>390</v>
+        <v>78</v>
       </c>
       <c r="J21" s="27" t="s">
         <v>394</v>
@@ -8598,42 +8595,42 @@
         <v>394</v>
       </c>
       <c r="L21" s="54" t="s">
-        <v>1088</v>
+        <v>818</v>
       </c>
       <c r="M21" t="str">
-        <f t="shared" si="2"/>
-        <v>Screened Topsoil</v>
+        <f>IFERROR(TRIM(LEFT(C21,SEARCH("(",C21)-1)),C21)</f>
+        <v>Sand</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="24">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f>VLOOKUP(B22,CatLU,3,FALSE)</f>
+        <v>30</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="C22" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>Yard - Grass,Leaves,Woodchips (In)</v>
-      </c>
-      <c r="D22" s="27" t="s">
-        <v>394</v>
-      </c>
-      <c r="E22" s="27" t="s">
-        <v>394</v>
-      </c>
-      <c r="F22" s="27" t="s">
-        <v>394</v>
-      </c>
-      <c r="G22" s="27" t="s">
-        <v>394</v>
-      </c>
-      <c r="H22" s="27" t="s">
-        <v>394</v>
-      </c>
-      <c r="I22" s="27" t="s">
-        <v>394</v>
+        <f>VLOOKUP(B22,Material,2,FALSE)</f>
+        <v>Sand Screened (OUT)</v>
+      </c>
+      <c r="D22" s="27">
+        <v>90</v>
+      </c>
+      <c r="E22" s="27">
+        <v>108</v>
+      </c>
+      <c r="F22" s="27">
+        <v>144</v>
+      </c>
+      <c r="G22" s="27">
+        <v>198</v>
+      </c>
+      <c r="H22" s="27">
+        <v>216</v>
+      </c>
+      <c r="I22" s="27">
+        <v>234</v>
       </c>
       <c r="J22" s="27" t="s">
         <v>394</v>
@@ -8641,43 +8638,43 @@
       <c r="K22" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="L22" s="55" t="s">
-        <v>821</v>
+      <c r="L22" s="54" t="s">
+        <v>1085</v>
       </c>
       <c r="M22" t="str">
-        <f t="shared" si="2"/>
-        <v>Yard - Grass,Leaves,Woodchips</v>
+        <f>IFERROR(TRIM(LEFT(C22,SEARCH("(",C22)-1)),C22)</f>
+        <v>Sand Screened</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="24">
-        <f t="shared" si="0"/>
-        <v>11</v>
+        <f>VLOOKUP(B23,CatLU,3,FALSE)</f>
+        <v>31</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="C23" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>Tree Stumps (In)</v>
-      </c>
-      <c r="D23" s="27" t="s">
-        <v>394</v>
-      </c>
-      <c r="E23" s="27" t="s">
-        <v>394</v>
-      </c>
-      <c r="F23" s="27" t="s">
-        <v>394</v>
-      </c>
-      <c r="G23" s="27" t="s">
-        <v>394</v>
-      </c>
-      <c r="H23" s="27" t="s">
-        <v>394</v>
-      </c>
-      <c r="I23" s="27" t="s">
-        <v>394</v>
+        <f>VLOOKUP(B23,Material,2,FALSE)</f>
+        <v>Screened Topsoil (OUT)</v>
+      </c>
+      <c r="D23" s="27">
+        <v>150</v>
+      </c>
+      <c r="E23" s="27">
+        <v>180</v>
+      </c>
+      <c r="F23" s="27">
+        <v>240</v>
+      </c>
+      <c r="G23" s="27">
+        <v>330</v>
+      </c>
+      <c r="H23" s="27">
+        <v>360</v>
+      </c>
+      <c r="I23" s="27">
+        <v>390</v>
       </c>
       <c r="J23" s="27" t="s">
         <v>394</v>
@@ -8685,157 +8682,155 @@
       <c r="K23" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="L23" s="55" t="s">
-        <v>821</v>
+      <c r="L23" s="54" t="s">
+        <v>1085</v>
       </c>
       <c r="M23" t="str">
-        <f t="shared" si="2"/>
-        <v>Tree Stumps</v>
+        <f>IFERROR(TRIM(LEFT(C23,SEARCH("(",C23)-1)),C23)</f>
+        <v>Screened Topsoil</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="24">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="B24" s="25">
-        <v>304</v>
+        <f>VLOOKUP(B24,CatLU,3,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="B24" s="56" t="s">
+        <v>402</v>
       </c>
       <c r="C24" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>#304 Limestone (Out)</v>
-      </c>
-      <c r="D24" s="27">
-        <v>350</v>
-      </c>
-      <c r="E24" s="27">
-        <v>420</v>
-      </c>
-      <c r="F24" s="27">
-        <v>560</v>
-      </c>
-      <c r="G24" s="27">
-        <v>770</v>
-      </c>
-      <c r="H24" s="27">
-        <v>840</v>
-      </c>
-      <c r="I24" s="27">
-        <v>910</v>
-      </c>
-      <c r="J24" s="27" t="s">
+        <f>VLOOKUP(B24,Material,2,FALSE)</f>
+        <v>Slop (IN)</v>
+      </c>
+      <c r="D24" s="57">
+        <v>500</v>
+      </c>
+      <c r="E24" s="57">
+        <v>600</v>
+      </c>
+      <c r="F24" s="57">
+        <v>800</v>
+      </c>
+      <c r="G24" s="57">
+        <v>1100</v>
+      </c>
+      <c r="H24" s="57">
+        <v>1200</v>
+      </c>
+      <c r="I24" s="57">
+        <v>1300</v>
+      </c>
+      <c r="J24" s="57">
+        <v>500</v>
+      </c>
+      <c r="K24" s="57" t="s">
         <v>394</v>
       </c>
-      <c r="K24" s="27" t="s">
-        <v>394</v>
-      </c>
       <c r="L24" s="54" t="s">
-        <v>1088</v>
+        <v>818</v>
       </c>
       <c r="M24" t="str">
-        <f t="shared" si="2"/>
-        <v>#304 Limestone</v>
+        <f>IFERROR(TRIM(LEFT(C24,SEARCH("(",C24)-1)),C24)</f>
+        <v>Slop</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="24">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="B25" s="25">
-        <v>57</v>
+        <f>VLOOKUP(B25,CatLU,3,FALSE)</f>
+        <v>80</v>
+      </c>
+      <c r="B25" s="31" t="s">
+        <v>416</v>
       </c>
       <c r="C25" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>#57 Limestone (Out)</v>
-      </c>
-      <c r="D25" s="27">
-        <v>400</v>
-      </c>
-      <c r="E25" s="27">
-        <v>480</v>
-      </c>
-      <c r="F25" s="27">
-        <v>640</v>
-      </c>
-      <c r="G25" s="27">
-        <v>880</v>
-      </c>
-      <c r="H25" s="27">
-        <v>960</v>
-      </c>
-      <c r="I25" s="27">
-        <v>1040</v>
-      </c>
-      <c r="J25" s="27" t="s">
+        <f>VLOOKUP(B25,Material,2,FALSE)</f>
+        <v>Snow In</v>
+      </c>
+      <c r="D25" s="32">
+        <v>25</v>
+      </c>
+      <c r="E25" s="32">
+        <v>30</v>
+      </c>
+      <c r="F25" s="32">
+        <v>40</v>
+      </c>
+      <c r="G25" s="32">
+        <v>55</v>
+      </c>
+      <c r="H25" s="32">
+        <v>60</v>
+      </c>
+      <c r="I25" s="32">
+        <v>65</v>
+      </c>
+      <c r="J25" s="32" t="s">
         <v>394</v>
       </c>
-      <c r="K25" s="27" t="s">
+      <c r="K25" s="32" t="s">
         <v>394</v>
       </c>
       <c r="L25" s="54" t="s">
-        <v>1088</v>
+        <v>818</v>
       </c>
       <c r="M25" t="str">
-        <f t="shared" si="2"/>
-        <v>#57 Limestone</v>
+        <f>IFERROR(TRIM(LEFT(C25,SEARCH("(",C25)-1)),C25)</f>
+        <v>Snow In</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="24">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="B26" s="29">
-        <v>10</v>
+        <f>VLOOKUP(B26,CatLU,3,FALSE)</f>
+        <v>11</v>
+      </c>
+      <c r="B26" s="56" t="s">
+        <v>412</v>
       </c>
       <c r="C26" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>#10 Limestone (Out)</v>
-      </c>
-      <c r="D26" s="30">
-        <v>350</v>
-      </c>
-      <c r="E26" s="30">
-        <v>420</v>
-      </c>
-      <c r="F26" s="30">
-        <v>560</v>
-      </c>
-      <c r="G26" s="30">
-        <v>770</v>
-      </c>
-      <c r="H26" s="30">
-        <v>840</v>
-      </c>
-      <c r="I26" s="30">
-        <v>910</v>
-      </c>
-      <c r="J26" s="30" t="s">
+        <f>VLOOKUP(B26,Material,2,FALSE)</f>
+        <v>Tree Stumps (In)</v>
+      </c>
+      <c r="D26" s="57" t="s">
         <v>394</v>
       </c>
-      <c r="K26" s="30" t="s">
+      <c r="E26" s="57" t="s">
         <v>394</v>
       </c>
-      <c r="L26" s="54" t="s">
-        <v>1088</v>
+      <c r="F26" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="G26" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="H26" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="I26" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="J26" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="K26" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="L26" s="55" t="s">
+        <v>818</v>
       </c>
       <c r="M26" t="str">
-        <f t="shared" si="2"/>
-        <v>#10 Limestone</v>
+        <f>IFERROR(TRIM(LEFT(C26,SEARCH("(",C26)-1)),C26)</f>
+        <v>Tree Stumps</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="24">
-        <f>VLOOKUP(B27,CatLU,3,FALSE)</f>
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>416</v>
-      </c>
-      <c r="C27" s="26" t="str">
-        <f>VLOOKUP(B27,Material,2,FALSE)</f>
-        <v>#304 Recycled Concrete (Out)</v>
+        <v>417</v>
+      </c>
+      <c r="C27" s="26" t="s">
+        <v>418</v>
       </c>
       <c r="D27" s="32">
         <v>125</v>
@@ -8862,197 +8857,70 @@
         <v>394</v>
       </c>
       <c r="L27" s="54" t="s">
-        <v>1088</v>
+        <v>818</v>
       </c>
       <c r="M27" t="str">
-        <f t="shared" si="2"/>
-        <v>#304 Recycled Concrete</v>
+        <f>IFERROR(TRIM(LEFT(C27,SEARCH("(",C27)-1)),C27)</f>
+        <v>Wet Dirt w/ Organics</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="24">
         <f>VLOOKUP(B28,CatLU,3,FALSE)</f>
-        <v>41</v>
-      </c>
-      <c r="B28" s="31" t="s">
-        <v>417</v>
+        <v>10</v>
+      </c>
+      <c r="B28" s="56" t="s">
+        <v>411</v>
       </c>
       <c r="C28" s="26" t="str">
         <f>VLOOKUP(B28,Material,2,FALSE)</f>
-        <v>#1&amp;2 Recycled Concrete (Out)</v>
-      </c>
-      <c r="D28" s="32">
-        <v>140</v>
-      </c>
-      <c r="E28" s="32">
-        <v>168</v>
-      </c>
-      <c r="F28" s="32">
-        <v>224</v>
-      </c>
-      <c r="G28" s="32">
-        <v>308</v>
-      </c>
-      <c r="H28" s="32">
-        <v>336</v>
-      </c>
-      <c r="I28" s="32">
-        <v>364</v>
-      </c>
-      <c r="J28" s="32" t="s">
+        <v>Yard - Grass,Leaves,Woodchips (In)</v>
+      </c>
+      <c r="D28" s="57" t="s">
         <v>394</v>
       </c>
-      <c r="K28" s="32" t="s">
+      <c r="E28" s="57" t="s">
         <v>394</v>
       </c>
-      <c r="L28" s="54" t="s">
-        <v>1088</v>
+      <c r="F28" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="G28" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="H28" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="I28" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="J28" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="K28" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="L28" s="55" t="s">
+        <v>818</v>
       </c>
       <c r="M28" t="str">
-        <f t="shared" si="2"/>
-        <v>#1&amp;2 Recycled Concrete</v>
+        <f>IFERROR(TRIM(LEFT(C28,SEARCH("(",C28)-1)),C28)</f>
+        <v>Yard - Grass,Leaves,Woodchips</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="24">
-        <f>VLOOKUP(B29,CatLU,3,FALSE)</f>
-        <v>42</v>
-      </c>
-      <c r="B29" s="31" t="s">
-        <v>418</v>
-      </c>
-      <c r="C29" s="26" t="str">
-        <f>VLOOKUP(B29,Material,2,FALSE)</f>
-        <v>#57 Recycled Concrete (Out)</v>
-      </c>
-      <c r="D29" s="32">
-        <v>150</v>
-      </c>
-      <c r="E29" s="32">
-        <v>180</v>
-      </c>
-      <c r="F29" s="32">
-        <v>240</v>
-      </c>
-      <c r="G29" s="32">
-        <v>330</v>
-      </c>
-      <c r="H29" s="32">
-        <v>360</v>
-      </c>
-      <c r="I29" s="32">
-        <v>390</v>
-      </c>
-      <c r="J29" s="32" t="s">
-        <v>394</v>
-      </c>
-      <c r="K29" s="32" t="s">
-        <v>394</v>
-      </c>
-      <c r="L29" s="54" t="s">
-        <v>1088</v>
-      </c>
-      <c r="M29" t="str">
-        <f t="shared" si="2"/>
-        <v>#57 Recycled Concrete</v>
-      </c>
+      <c r="L29" s="54"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="24">
-        <f>VLOOKUP(B30,CatLU,3,FALSE)</f>
-        <v>80</v>
-      </c>
-      <c r="B30" s="31" t="s">
-        <v>419</v>
-      </c>
-      <c r="C30" s="26" t="str">
-        <f>VLOOKUP(B30,Material,2,FALSE)</f>
-        <v>Snow In</v>
-      </c>
-      <c r="D30" s="32">
-        <v>25</v>
-      </c>
-      <c r="E30" s="32">
-        <v>30</v>
-      </c>
-      <c r="F30" s="32">
-        <v>40</v>
-      </c>
-      <c r="G30" s="32">
-        <v>55</v>
-      </c>
-      <c r="H30" s="32">
-        <v>60</v>
-      </c>
-      <c r="I30" s="32">
-        <v>65</v>
-      </c>
-      <c r="J30" s="32" t="s">
-        <v>394</v>
-      </c>
-      <c r="K30" s="32" t="s">
-        <v>394</v>
-      </c>
-      <c r="L30" s="54" t="s">
-        <v>821</v>
-      </c>
-      <c r="M30" t="str">
-        <f t="shared" si="2"/>
-        <v>Snow In</v>
-      </c>
+      <c r="L30" s="54"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="24">
-        <v>14</v>
-      </c>
-      <c r="B31" s="31" t="s">
-        <v>420</v>
-      </c>
-      <c r="C31" s="26" t="s">
-        <v>421</v>
-      </c>
-      <c r="D31" s="32">
-        <v>125</v>
-      </c>
-      <c r="E31" s="32">
-        <v>150</v>
-      </c>
-      <c r="F31" s="32">
-        <v>200</v>
-      </c>
-      <c r="G31" s="32">
-        <v>275</v>
-      </c>
-      <c r="H31" s="32">
-        <v>300</v>
-      </c>
-      <c r="I31" s="32">
-        <v>325</v>
-      </c>
-      <c r="J31" s="32" t="s">
-        <v>394</v>
-      </c>
-      <c r="K31" s="32" t="s">
-        <v>394</v>
-      </c>
-      <c r="L31" s="54" t="s">
-        <v>821</v>
-      </c>
-      <c r="M31" t="str">
-        <f t="shared" si="2"/>
-        <v>Wet Dirt w/ Organics</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L32" s="54"/>
-    </row>
-    <row r="33" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L33" s="54"/>
-    </row>
-    <row r="34" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L34" s="54"/>
+      <c r="L31" s="54"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M31">
+    <sortCondition ref="C1:C31"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9075,31 +8943,31 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C1" t="s">
+        <v>421</v>
+      </c>
+      <c r="D1" t="s">
         <v>422</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>423</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>424</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>425</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>426</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" s="33" t="s">
         <v>427</v>
-      </c>
-      <c r="G1" t="s">
-        <v>428</v>
-      </c>
-      <c r="H1" t="s">
-        <v>429</v>
-      </c>
-      <c r="I1" s="33" t="s">
-        <v>430</v>
       </c>
       <c r="J1" t="s">
         <v>2</v>
@@ -9107,16 +8975,16 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G2">
         <v>44319</v>
@@ -9125,20 +8993,20 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D3" s="34"/>
       <c r="E3" s="34" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F3" s="34" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G3" s="34">
         <v>44306</v>
@@ -9149,20 +9017,20 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="34" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B4" s="34" t="s">
+        <v>433</v>
+      </c>
+      <c r="C4" s="34" t="s">
         <v>436</v>
-      </c>
-      <c r="C4" s="34" t="s">
-        <v>439</v>
       </c>
       <c r="D4" s="34"/>
       <c r="E4" s="34" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F4" s="34" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G4" s="34">
         <v>44306</v>
@@ -9170,24 +9038,24 @@
       <c r="H4" s="34"/>
       <c r="I4" s="35"/>
       <c r="J4" s="36" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>438</v>
+      </c>
+      <c r="B5" t="s">
+        <v>439</v>
+      </c>
+      <c r="C5" t="s">
+        <v>440</v>
+      </c>
+      <c r="E5" t="s">
         <v>441</v>
       </c>
-      <c r="B5" t="s">
-        <v>442</v>
-      </c>
-      <c r="C5" t="s">
-        <v>443</v>
-      </c>
-      <c r="E5" t="s">
-        <v>444</v>
-      </c>
       <c r="F5" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G5">
         <v>44135</v>
@@ -9198,49 +9066,49 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="34" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D6" s="34"/>
       <c r="E6" s="34" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F6" s="34" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G6" s="34">
         <v>44048</v>
       </c>
       <c r="H6" s="34" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="I6" s="35">
         <v>4403067884</v>
       </c>
       <c r="J6" s="37" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>448</v>
+      </c>
+      <c r="B7" t="s">
+        <v>449</v>
+      </c>
+      <c r="C7" t="s">
+        <v>450</v>
+      </c>
+      <c r="E7" t="s">
         <v>451</v>
       </c>
-      <c r="B7" t="s">
-        <v>452</v>
-      </c>
-      <c r="C7" t="s">
-        <v>453</v>
-      </c>
-      <c r="E7" t="s">
-        <v>454</v>
-      </c>
       <c r="F7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G7">
         <v>44133</v>
@@ -9251,57 +9119,57 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>452</v>
+      </c>
+      <c r="B8" t="s">
+        <v>453</v>
+      </c>
+      <c r="C8" t="s">
+        <v>454</v>
+      </c>
+      <c r="E8" t="s">
         <v>455</v>
       </c>
-      <c r="B8" t="s">
-        <v>456</v>
-      </c>
-      <c r="C8" t="s">
-        <v>457</v>
-      </c>
-      <c r="E8" t="s">
-        <v>458</v>
-      </c>
       <c r="F8" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G8">
         <v>44132</v>
       </c>
       <c r="H8" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="I8" s="33">
         <v>2162896600</v>
       </c>
       <c r="J8" s="38" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>458</v>
+      </c>
+      <c r="B9" t="s">
+        <v>459</v>
+      </c>
+      <c r="C9" t="s">
+        <v>460</v>
+      </c>
+      <c r="D9" t="s">
         <v>461</v>
       </c>
-      <c r="B9" t="s">
+      <c r="E9" t="s">
         <v>462</v>
       </c>
-      <c r="C9" t="s">
-        <v>463</v>
-      </c>
-      <c r="D9" t="s">
-        <v>464</v>
-      </c>
-      <c r="E9" t="s">
-        <v>465</v>
-      </c>
       <c r="F9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G9">
         <v>44203</v>
       </c>
       <c r="H9" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I9" s="33">
         <v>3307534722</v>
@@ -9310,57 +9178,57 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>464</v>
+      </c>
+      <c r="B10" t="s">
+        <v>465</v>
+      </c>
+      <c r="C10" t="s">
+        <v>466</v>
+      </c>
+      <c r="E10" t="s">
         <v>467</v>
       </c>
-      <c r="B10" t="s">
-        <v>468</v>
-      </c>
-      <c r="C10" t="s">
-        <v>469</v>
-      </c>
-      <c r="E10" t="s">
-        <v>470</v>
-      </c>
       <c r="F10" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G10">
         <v>44026</v>
       </c>
       <c r="H10" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="I10" s="33">
         <v>4403361590</v>
       </c>
       <c r="J10" s="39" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B11" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="I11" s="33"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>472</v>
+      </c>
+      <c r="B12" t="s">
+        <v>473</v>
+      </c>
+      <c r="C12" t="s">
+        <v>474</v>
+      </c>
+      <c r="E12" t="s">
         <v>475</v>
       </c>
-      <c r="B12" t="s">
-        <v>476</v>
-      </c>
-      <c r="C12" t="s">
-        <v>477</v>
-      </c>
-      <c r="E12" t="s">
-        <v>478</v>
-      </c>
       <c r="F12" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G12">
         <v>44033</v>
@@ -9369,124 +9237,124 @@
         <v>8003621343</v>
       </c>
       <c r="J12" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>477</v>
+      </c>
+      <c r="B13" t="s">
+        <v>478</v>
+      </c>
+      <c r="C13" t="s">
+        <v>479</v>
+      </c>
+      <c r="E13" t="s">
         <v>480</v>
       </c>
-      <c r="B13" t="s">
-        <v>481</v>
-      </c>
-      <c r="C13" t="s">
-        <v>482</v>
-      </c>
-      <c r="E13" t="s">
-        <v>483</v>
-      </c>
       <c r="F13" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G13">
         <v>44125</v>
       </c>
       <c r="H13" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="I13" s="33">
         <v>2168232244</v>
       </c>
       <c r="J13" s="38" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="40" t="s">
+        <v>483</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>484</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>485</v>
+      </c>
+      <c r="D14" s="34" t="s">
         <v>486</v>
       </c>
-      <c r="B14" s="34" t="s">
-        <v>487</v>
-      </c>
-      <c r="C14" s="34" t="s">
-        <v>488</v>
-      </c>
-      <c r="D14" s="34" t="s">
-        <v>489</v>
-      </c>
       <c r="E14" s="34" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G14" s="34">
         <v>44105</v>
       </c>
       <c r="H14" s="34" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="I14" s="35" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="J14" s="41" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B15" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="I15" s="33"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="40" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C16" s="40" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D16" s="40"/>
       <c r="E16" s="40" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F16" s="40" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G16" s="40">
         <v>44278</v>
       </c>
       <c r="H16" s="40" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="I16" s="42">
         <v>3308199559</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>496</v>
+      </c>
+      <c r="B17" t="s">
+        <v>497</v>
+      </c>
+      <c r="C17" t="s">
+        <v>498</v>
+      </c>
+      <c r="E17" t="s">
         <v>499</v>
       </c>
-      <c r="B17" t="s">
-        <v>500</v>
-      </c>
-      <c r="C17" t="s">
-        <v>501</v>
-      </c>
-      <c r="E17" t="s">
-        <v>502</v>
-      </c>
       <c r="F17" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G17">
         <v>44137</v>
@@ -9495,49 +9363,49 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>500</v>
+      </c>
+      <c r="B18" t="s">
+        <v>501</v>
+      </c>
+      <c r="C18" t="s">
+        <v>502</v>
+      </c>
+      <c r="E18" t="s">
         <v>503</v>
       </c>
-      <c r="B18" t="s">
-        <v>504</v>
-      </c>
-      <c r="C18" t="s">
-        <v>505</v>
-      </c>
-      <c r="E18" t="s">
-        <v>506</v>
-      </c>
       <c r="F18" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G18">
         <v>44265</v>
       </c>
       <c r="H18" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="I18" s="33" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="J18" s="38" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="40" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B19" s="40" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="C19" s="40" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="D19" s="40"/>
       <c r="E19" s="40" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F19" s="40" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G19" s="40">
         <v>44278</v>
@@ -9547,59 +9415,59 @@
         <v>3308199559</v>
       </c>
       <c r="J19" s="37" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>510</v>
+      </c>
+      <c r="B20" t="s">
+        <v>511</v>
+      </c>
+      <c r="C20" t="s">
+        <v>512</v>
+      </c>
+      <c r="E20" t="s">
         <v>513</v>
       </c>
-      <c r="B20" t="s">
-        <v>514</v>
-      </c>
-      <c r="C20" t="s">
-        <v>515</v>
-      </c>
-      <c r="E20" t="s">
-        <v>516</v>
-      </c>
       <c r="F20" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G20">
         <v>44203</v>
       </c>
       <c r="H20" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="I20" s="33" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="J20" s="38" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>517</v>
+      </c>
+      <c r="B21" t="s">
+        <v>518</v>
+      </c>
+      <c r="C21" t="s">
+        <v>519</v>
+      </c>
+      <c r="E21" t="s">
         <v>520</v>
       </c>
-      <c r="B21" t="s">
-        <v>521</v>
-      </c>
-      <c r="C21" t="s">
-        <v>522</v>
-      </c>
-      <c r="E21" t="s">
-        <v>523</v>
-      </c>
       <c r="F21" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G21">
         <v>44147</v>
       </c>
       <c r="H21" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="I21" s="33">
         <v>4405262622</v>
@@ -9607,19 +9475,19 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B22" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C22" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E22" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F22" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G22">
         <v>44026</v>
@@ -9628,151 +9496,151 @@
         <v>4407292122</v>
       </c>
       <c r="J22" s="38" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="43" t="s">
+        <v>526</v>
+      </c>
+      <c r="B23" s="43" t="s">
+        <v>527</v>
+      </c>
+      <c r="C23" s="43" t="s">
+        <v>528</v>
+      </c>
+      <c r="D23" s="43" t="s">
         <v>529</v>
       </c>
-      <c r="B23" s="43" t="s">
+      <c r="E23" s="43" t="s">
         <v>530</v>
       </c>
-      <c r="C23" s="43" t="s">
-        <v>531</v>
-      </c>
-      <c r="D23" s="43" t="s">
-        <v>532</v>
-      </c>
-      <c r="E23" s="43" t="s">
-        <v>533</v>
-      </c>
       <c r="F23" s="43" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G23" s="43">
         <v>44256</v>
       </c>
       <c r="H23" s="44"/>
       <c r="I23" s="45" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="J23" s="44" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>533</v>
+      </c>
+      <c r="B24" t="s">
+        <v>534</v>
+      </c>
+      <c r="C24" t="s">
+        <v>535</v>
+      </c>
+      <c r="E24" t="s">
         <v>536</v>
       </c>
-      <c r="B24" t="s">
-        <v>537</v>
-      </c>
-      <c r="C24" t="s">
-        <v>538</v>
-      </c>
-      <c r="E24" t="s">
-        <v>539</v>
-      </c>
       <c r="F24" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G24">
         <v>44023</v>
       </c>
       <c r="H24" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="I24" s="33" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="40" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B25" s="34" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C25" s="34" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D25" s="34"/>
       <c r="E25" s="34" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="F25" s="34" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G25" s="34">
         <v>44065</v>
       </c>
       <c r="H25" s="41" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="I25" s="35">
         <v>4405641011</v>
       </c>
       <c r="J25" s="37" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="B26" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="C26" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="E26" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="F26" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G26">
         <v>44141</v>
       </c>
       <c r="H26" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="I26" s="33">
         <v>2167549626</v>
       </c>
       <c r="J26" s="38" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="B27" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C27" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="I27" s="33"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>552</v>
+      </c>
+      <c r="B28" t="s">
+        <v>553</v>
+      </c>
+      <c r="C28" t="s">
+        <v>554</v>
+      </c>
+      <c r="E28" t="s">
         <v>555</v>
       </c>
-      <c r="B28" t="s">
-        <v>556</v>
-      </c>
-      <c r="C28" t="s">
-        <v>557</v>
-      </c>
-      <c r="E28" t="s">
-        <v>558</v>
-      </c>
       <c r="F28" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G28">
         <v>44146</v>
@@ -9783,57 +9651,57 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>556</v>
+      </c>
+      <c r="B29" t="s">
+        <v>557</v>
+      </c>
+      <c r="C29" t="s">
+        <v>558</v>
+      </c>
+      <c r="E29" t="s">
         <v>559</v>
       </c>
-      <c r="B29" t="s">
-        <v>560</v>
-      </c>
-      <c r="C29" t="s">
-        <v>561</v>
-      </c>
-      <c r="E29" t="s">
-        <v>562</v>
-      </c>
       <c r="F29" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G29">
         <v>44012</v>
       </c>
       <c r="H29" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="I29" s="33">
         <v>2164692440</v>
       </c>
       <c r="J29" s="38" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B30" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="I30" s="33"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>564</v>
+      </c>
+      <c r="B31" t="s">
+        <v>565</v>
+      </c>
+      <c r="C31" t="s">
+        <v>566</v>
+      </c>
+      <c r="E31" t="s">
         <v>567</v>
       </c>
-      <c r="B31" t="s">
-        <v>568</v>
-      </c>
-      <c r="C31" t="s">
-        <v>569</v>
-      </c>
-      <c r="E31" t="s">
-        <v>570</v>
-      </c>
       <c r="F31" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G31">
         <v>44021</v>
@@ -9844,19 +9712,19 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="B32" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C32" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="E32" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="F32" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G32">
         <v>44012</v>
@@ -9867,67 +9735,67 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B33" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="I33" s="33"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B34" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="I34" s="33"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>575</v>
+      </c>
+      <c r="B35" t="s">
+        <v>576</v>
+      </c>
+      <c r="C35" t="s">
+        <v>577</v>
+      </c>
+      <c r="E35" t="s">
         <v>578</v>
       </c>
-      <c r="B35" t="s">
-        <v>579</v>
-      </c>
-      <c r="C35" t="s">
-        <v>580</v>
-      </c>
-      <c r="E35" t="s">
-        <v>581</v>
-      </c>
       <c r="F35" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G35">
         <v>44125</v>
       </c>
       <c r="H35" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="I35" s="33"/>
       <c r="J35" s="38" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>581</v>
+      </c>
+      <c r="B36" t="s">
+        <v>582</v>
+      </c>
+      <c r="C36" t="s">
+        <v>583</v>
+      </c>
+      <c r="D36" t="s">
         <v>584</v>
       </c>
-      <c r="B36" t="s">
+      <c r="E36" t="s">
         <v>585</v>
       </c>
-      <c r="C36" t="s">
-        <v>586</v>
-      </c>
-      <c r="D36" t="s">
-        <v>587</v>
-      </c>
-      <c r="E36" t="s">
-        <v>588</v>
-      </c>
       <c r="F36" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G36">
         <v>44094</v>
@@ -9938,19 +9806,19 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>586</v>
+      </c>
+      <c r="B37" t="s">
+        <v>587</v>
+      </c>
+      <c r="C37" t="s">
+        <v>588</v>
+      </c>
+      <c r="E37" t="s">
         <v>589</v>
       </c>
-      <c r="B37" t="s">
-        <v>590</v>
-      </c>
-      <c r="C37" t="s">
-        <v>591</v>
-      </c>
-      <c r="E37" t="s">
-        <v>592</v>
-      </c>
       <c r="F37" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G37">
         <v>44124</v>
@@ -9959,19 +9827,19 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>590</v>
+      </c>
+      <c r="B38" t="s">
+        <v>591</v>
+      </c>
+      <c r="C38" t="s">
+        <v>592</v>
+      </c>
+      <c r="E38" t="s">
         <v>593</v>
       </c>
-      <c r="B38" t="s">
-        <v>594</v>
-      </c>
-      <c r="C38" t="s">
-        <v>595</v>
-      </c>
-      <c r="E38" t="s">
-        <v>596</v>
-      </c>
       <c r="F38" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G38">
         <v>44131</v>
@@ -9980,24 +9848,24 @@
         <v>2162677705</v>
       </c>
       <c r="J38" s="38" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>595</v>
+      </c>
+      <c r="B39" t="s">
+        <v>596</v>
+      </c>
+      <c r="C39" t="s">
+        <v>597</v>
+      </c>
+      <c r="E39" t="s">
         <v>598</v>
       </c>
-      <c r="B39" t="s">
-        <v>599</v>
-      </c>
-      <c r="C39" t="s">
-        <v>600</v>
-      </c>
-      <c r="E39" t="s">
-        <v>601</v>
-      </c>
       <c r="F39" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G39">
         <v>44145</v>
@@ -10008,45 +9876,45 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>599</v>
+      </c>
+      <c r="B40" t="s">
+        <v>600</v>
+      </c>
+      <c r="C40" t="s">
+        <v>601</v>
+      </c>
+      <c r="E40" t="s">
         <v>602</v>
       </c>
-      <c r="B40" t="s">
-        <v>603</v>
-      </c>
-      <c r="C40" t="s">
-        <v>604</v>
-      </c>
-      <c r="E40" t="s">
-        <v>605</v>
-      </c>
       <c r="F40" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G40">
         <v>44022</v>
       </c>
       <c r="I40" s="33" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="J40" s="46" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B41" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C41" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="E41" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F41" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G41">
         <v>44125</v>
@@ -10055,19 +9923,19 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B42" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C42" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="E42" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F42" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G42">
         <v>44125</v>
@@ -10078,25 +9946,25 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B43" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C43" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="E43" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="F43" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G43">
         <v>441461006</v>
       </c>
       <c r="H43" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="I43" s="33">
         <v>2165818600</v>
@@ -10104,19 +9972,19 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="B44" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C44" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="E44" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F44" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G44">
         <v>44133</v>
@@ -10125,25 +9993,25 @@
         <v>4402373292</v>
       </c>
       <c r="J44" s="38" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="43" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B45" s="43" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C45" s="43" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="D45" s="43"/>
       <c r="E45" s="43" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="F45" s="43" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G45" s="43">
         <v>44256</v>
@@ -10153,27 +10021,27 @@
         <v>3302392379</v>
       </c>
       <c r="J45" s="44" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>623</v>
+      </c>
+      <c r="B46" t="s">
+        <v>624</v>
+      </c>
+      <c r="C46" t="s">
+        <v>625</v>
+      </c>
+      <c r="D46" t="s">
         <v>626</v>
       </c>
-      <c r="B46" t="s">
+      <c r="E46" t="s">
         <v>627</v>
       </c>
-      <c r="C46" t="s">
-        <v>628</v>
-      </c>
-      <c r="D46" t="s">
-        <v>629</v>
-      </c>
-      <c r="E46" t="s">
-        <v>630</v>
-      </c>
       <c r="F46" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G46">
         <v>44131</v>
@@ -10182,45 +10050,45 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>628</v>
+      </c>
+      <c r="B47" t="s">
+        <v>629</v>
+      </c>
+      <c r="C47" t="s">
+        <v>630</v>
+      </c>
+      <c r="E47" t="s">
         <v>631</v>
       </c>
-      <c r="B47" t="s">
-        <v>632</v>
-      </c>
-      <c r="C47" t="s">
-        <v>633</v>
-      </c>
-      <c r="E47" t="s">
-        <v>634</v>
-      </c>
       <c r="F47" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G47">
         <v>44060</v>
       </c>
       <c r="I47" s="33" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="J47" s="38" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B48" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C48" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="E48" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F48" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G48">
         <v>44026</v>
@@ -10231,77 +10099,77 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>637</v>
+      </c>
+      <c r="B49" t="s">
+        <v>638</v>
+      </c>
+      <c r="C49" t="s">
+        <v>639</v>
+      </c>
+      <c r="E49" t="s">
         <v>640</v>
       </c>
-      <c r="B49" t="s">
-        <v>641</v>
-      </c>
-      <c r="C49" t="s">
-        <v>642</v>
-      </c>
-      <c r="E49" t="s">
-        <v>643</v>
-      </c>
       <c r="F49" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G49">
         <v>44460</v>
       </c>
       <c r="H49" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="I49" s="33" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="J49" s="38" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>644</v>
+      </c>
+      <c r="B50" t="s">
+        <v>645</v>
+      </c>
+      <c r="C50" t="s">
+        <v>646</v>
+      </c>
+      <c r="E50" t="s">
         <v>647</v>
       </c>
-      <c r="B50" t="s">
-        <v>648</v>
-      </c>
-      <c r="C50" t="s">
-        <v>649</v>
-      </c>
-      <c r="E50" t="s">
-        <v>650</v>
-      </c>
       <c r="F50" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G50">
         <v>44240</v>
       </c>
       <c r="H50" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="I50" s="33">
         <v>3306735501</v>
       </c>
       <c r="J50" s="38" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="B51" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="C51" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="E51" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F51" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G51">
         <v>44125</v>
@@ -10312,19 +10180,19 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B52" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="C52" s="47" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="E52" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F52" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G52">
         <v>44103</v>
@@ -10335,19 +10203,19 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="B53" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="C53" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="E53" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F53" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G53">
         <v>44128</v>
@@ -10356,53 +10224,53 @@
         <v>2165811000</v>
       </c>
       <c r="J53" s="38" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>660</v>
+      </c>
+      <c r="B54" t="s">
+        <v>661</v>
+      </c>
+      <c r="C54" t="s">
+        <v>662</v>
+      </c>
+      <c r="E54" t="s">
         <v>663</v>
       </c>
-      <c r="B54" t="s">
-        <v>664</v>
-      </c>
-      <c r="C54" t="s">
-        <v>665</v>
-      </c>
-      <c r="E54" t="s">
-        <v>666</v>
-      </c>
       <c r="F54" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G54">
         <v>44024</v>
       </c>
       <c r="H54" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="I54" s="33">
         <v>2168702047</v>
       </c>
       <c r="J54" s="38" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="B55" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="C55" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="E55" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F55" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G55">
         <v>44135</v>
@@ -10413,20 +10281,20 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="40" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="B56" s="40" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C56" s="40" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="D56" s="40"/>
       <c r="E56" s="40" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F56" s="40" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G56" s="40">
         <v>44125</v>
@@ -10439,19 +10307,19 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>672</v>
+      </c>
+      <c r="B57" t="s">
+        <v>673</v>
+      </c>
+      <c r="C57" t="s">
+        <v>674</v>
+      </c>
+      <c r="E57" t="s">
         <v>675</v>
       </c>
-      <c r="B57" t="s">
-        <v>676</v>
-      </c>
-      <c r="C57" t="s">
-        <v>677</v>
-      </c>
-      <c r="E57" t="s">
-        <v>678</v>
-      </c>
       <c r="F57" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G57">
         <v>44720</v>
@@ -10462,31 +10330,31 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="B58" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="I58" s="33"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>678</v>
+      </c>
+      <c r="B59" t="s">
+        <v>679</v>
+      </c>
+      <c r="C59" t="s">
+        <v>680</v>
+      </c>
+      <c r="D59" t="s">
         <v>681</v>
       </c>
-      <c r="B59" t="s">
-        <v>682</v>
-      </c>
-      <c r="C59" t="s">
-        <v>683</v>
-      </c>
-      <c r="D59" t="s">
-        <v>684</v>
-      </c>
       <c r="E59" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="F59" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G59">
         <v>44065</v>
@@ -10497,19 +10365,19 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>682</v>
+      </c>
+      <c r="B60" t="s">
+        <v>683</v>
+      </c>
+      <c r="C60" t="s">
+        <v>684</v>
+      </c>
+      <c r="E60" t="s">
         <v>685</v>
       </c>
-      <c r="B60" t="s">
-        <v>686</v>
-      </c>
-      <c r="C60" t="s">
-        <v>687</v>
-      </c>
-      <c r="E60" t="s">
-        <v>688</v>
-      </c>
       <c r="F60" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G60">
         <v>44266</v>
@@ -10518,19 +10386,19 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B61" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="C61" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="E61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="F61" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G61">
         <v>44060</v>
@@ -10539,28 +10407,28 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B62" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="I62" s="33"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="B63" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="C63" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="E63" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F63" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G63">
         <v>44128</v>
@@ -10571,19 +10439,19 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B64" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C64" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="E64" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F64" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G64">
         <v>44135</v>
@@ -10592,82 +10460,82 @@
         <v>2166719333</v>
       </c>
       <c r="J64" s="38" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="B65" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="C65" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="E65" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="F65" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G65">
         <v>44141</v>
       </c>
       <c r="H65" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="I65" s="33">
         <v>4408233669</v>
       </c>
       <c r="J65" s="38" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>703</v>
+      </c>
+      <c r="B66" t="s">
+        <v>704</v>
+      </c>
+      <c r="C66" t="s">
+        <v>705</v>
+      </c>
+      <c r="E66" t="s">
         <v>706</v>
       </c>
-      <c r="B66" t="s">
-        <v>707</v>
-      </c>
-      <c r="C66" t="s">
-        <v>708</v>
-      </c>
-      <c r="E66" t="s">
-        <v>709</v>
-      </c>
       <c r="F66" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G66">
         <v>44067</v>
       </c>
       <c r="H66" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="I66" s="33" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="J66" s="38" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>709</v>
+      </c>
+      <c r="B67" t="s">
+        <v>710</v>
+      </c>
+      <c r="C67" t="s">
+        <v>711</v>
+      </c>
+      <c r="E67" t="s">
         <v>712</v>
       </c>
-      <c r="B67" t="s">
-        <v>713</v>
-      </c>
-      <c r="C67" t="s">
-        <v>714</v>
-      </c>
-      <c r="E67" t="s">
-        <v>715</v>
-      </c>
       <c r="F67" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G67">
         <v>44406</v>
@@ -10676,19 +10544,19 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="B68" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="C68" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="E68" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F68" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G68">
         <v>44278</v>
@@ -10699,39 +10567,39 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>716</v>
+      </c>
+      <c r="B69" t="s">
+        <v>717</v>
+      </c>
+      <c r="C69" t="s">
+        <v>718</v>
+      </c>
+      <c r="E69" t="s">
         <v>719</v>
       </c>
-      <c r="B69" t="s">
-        <v>720</v>
-      </c>
-      <c r="C69" t="s">
-        <v>721</v>
-      </c>
-      <c r="E69" t="s">
-        <v>722</v>
-      </c>
       <c r="F69" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G69">
         <v>44224</v>
       </c>
       <c r="H69" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="I69" s="33" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="J69" s="38" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="40" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="B70" s="34" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="C70" s="34"/>
       <c r="D70" s="34"/>
@@ -10744,19 +10612,19 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>725</v>
+      </c>
+      <c r="B71" t="s">
+        <v>726</v>
+      </c>
+      <c r="C71" t="s">
+        <v>727</v>
+      </c>
+      <c r="E71" t="s">
         <v>728</v>
       </c>
-      <c r="B71" t="s">
-        <v>729</v>
-      </c>
-      <c r="C71" t="s">
-        <v>730</v>
-      </c>
-      <c r="E71" t="s">
-        <v>731</v>
-      </c>
       <c r="F71" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G71">
         <v>44273</v>
@@ -10767,25 +10635,25 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>729</v>
+      </c>
+      <c r="B72" t="s">
+        <v>730</v>
+      </c>
+      <c r="C72" t="s">
+        <v>731</v>
+      </c>
+      <c r="E72" t="s">
         <v>732</v>
       </c>
-      <c r="B72" t="s">
-        <v>733</v>
-      </c>
-      <c r="C72" t="s">
-        <v>734</v>
-      </c>
-      <c r="E72" t="s">
-        <v>735</v>
-      </c>
       <c r="F72" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G72">
         <v>44095</v>
       </c>
       <c r="H72" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="I72" s="33">
         <v>4409512266</v>
@@ -10793,51 +10661,51 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>734</v>
+      </c>
+      <c r="B73" t="s">
+        <v>735</v>
+      </c>
+      <c r="C73" t="s">
+        <v>736</v>
+      </c>
+      <c r="D73" t="s">
         <v>737</v>
       </c>
-      <c r="B73" t="s">
+      <c r="E73" t="s">
         <v>738</v>
       </c>
-      <c r="C73" t="s">
-        <v>739</v>
-      </c>
-      <c r="D73" t="s">
-        <v>740</v>
-      </c>
-      <c r="E73" t="s">
-        <v>741</v>
-      </c>
       <c r="F73" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G73">
         <v>43019</v>
       </c>
       <c r="H73" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="I73" s="33" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="J73" s="38" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>742</v>
+      </c>
+      <c r="B74" t="s">
+        <v>743</v>
+      </c>
+      <c r="C74" t="s">
+        <v>744</v>
+      </c>
+      <c r="E74" t="s">
         <v>745</v>
       </c>
-      <c r="B74" t="s">
-        <v>746</v>
-      </c>
-      <c r="C74" t="s">
-        <v>747</v>
-      </c>
-      <c r="E74" t="s">
-        <v>748</v>
-      </c>
       <c r="F74" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G74">
         <v>44011</v>
@@ -10846,56 +10714,56 @@
         <v>4409341008</v>
       </c>
       <c r="J74" s="38" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B75" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="C75" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="E75" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="F75" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G75">
         <v>43019</v>
       </c>
       <c r="H75" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="I75" s="33">
         <v>7408484960</v>
       </c>
       <c r="J75" s="38" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>752</v>
+      </c>
+      <c r="B76" t="s">
+        <v>753</v>
+      </c>
+      <c r="C76" t="s">
+        <v>754</v>
+      </c>
+      <c r="D76" t="s">
         <v>755</v>
       </c>
-      <c r="B76" t="s">
+      <c r="E76" t="s">
         <v>756</v>
       </c>
-      <c r="C76" t="s">
-        <v>757</v>
-      </c>
-      <c r="D76" t="s">
-        <v>758</v>
-      </c>
-      <c r="E76" t="s">
-        <v>759</v>
-      </c>
       <c r="F76" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G76">
         <v>44212</v>
@@ -10906,48 +10774,48 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="B77" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="C77" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="E77" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F77" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G77">
         <v>44133</v>
       </c>
       <c r="H77" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="I77" s="33">
         <v>4402373292</v>
       </c>
       <c r="J77" s="48" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="B78" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="C78" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="E78" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="F78" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G78">
         <v>44131</v>
@@ -10958,46 +10826,46 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>763</v>
+      </c>
+      <c r="B79" t="s">
+        <v>764</v>
+      </c>
+      <c r="C79" t="s">
+        <v>765</v>
+      </c>
+      <c r="E79" t="s">
         <v>766</v>
       </c>
-      <c r="B79" t="s">
-        <v>767</v>
-      </c>
-      <c r="C79" t="s">
-        <v>768</v>
-      </c>
-      <c r="E79" t="s">
-        <v>769</v>
-      </c>
       <c r="F79" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G79">
         <v>44125</v>
       </c>
       <c r="I79" s="33" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="J79" s="38" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="40" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="B80" s="40" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C80" s="40" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="D80" s="40"/>
       <c r="E80" s="40" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F80" s="40" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G80" s="40">
         <v>44104</v>
@@ -11007,24 +10875,24 @@
         <v>4406281546</v>
       </c>
       <c r="J80" s="37" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>772</v>
+      </c>
+      <c r="B81" t="s">
+        <v>773</v>
+      </c>
+      <c r="C81" t="s">
+        <v>774</v>
+      </c>
+      <c r="E81" t="s">
         <v>775</v>
       </c>
-      <c r="B81" t="s">
-        <v>776</v>
-      </c>
-      <c r="C81" t="s">
-        <v>777</v>
-      </c>
-      <c r="E81" t="s">
-        <v>778</v>
-      </c>
       <c r="F81" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G81">
         <v>43055</v>
@@ -11036,19 +10904,19 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="B82" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="C82" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E82" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="F82" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G82">
         <v>44094</v>
@@ -11059,19 +10927,19 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="B83" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="C83" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="E83" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F83" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G83">
         <v>44124</v>
@@ -11082,72 +10950,72 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>782</v>
+      </c>
+      <c r="B84" t="s">
+        <v>783</v>
+      </c>
+      <c r="C84" t="s">
+        <v>784</v>
+      </c>
+      <c r="E84" t="s">
         <v>785</v>
       </c>
-      <c r="B84" t="s">
-        <v>786</v>
-      </c>
-      <c r="C84" t="s">
-        <v>787</v>
-      </c>
-      <c r="E84" t="s">
-        <v>788</v>
-      </c>
       <c r="F84" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G84">
         <v>44280</v>
       </c>
       <c r="I84" s="33" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="J84" s="38" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="B85" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="C85" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="E85" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F85" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G85">
         <v>44103</v>
       </c>
       <c r="I85" s="33" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="J85" s="38" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="40" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="B86" s="40" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="C86" s="40" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="D86" s="40"/>
       <c r="E86" s="40" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="F86" s="40" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G86" s="40">
         <v>44146</v>
@@ -11157,30 +11025,30 @@
         <v>4404394900</v>
       </c>
       <c r="J86" s="37" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>797</v>
+      </c>
+      <c r="B87" t="s">
+        <v>798</v>
+      </c>
+      <c r="C87" t="s">
+        <v>799</v>
+      </c>
+      <c r="E87" t="s">
         <v>800</v>
       </c>
-      <c r="B87" t="s">
-        <v>801</v>
-      </c>
-      <c r="C87" t="s">
-        <v>802</v>
-      </c>
-      <c r="E87" t="s">
-        <v>803</v>
-      </c>
       <c r="F87" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G87">
         <v>44511</v>
       </c>
       <c r="H87" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="I87" s="33">
         <v>3307742468</v>
@@ -11188,31 +11056,31 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>802</v>
+      </c>
+      <c r="B88" t="s">
+        <v>803</v>
+      </c>
+      <c r="C88" t="s">
+        <v>804</v>
+      </c>
+      <c r="E88" t="s">
         <v>805</v>
       </c>
-      <c r="B88" t="s">
-        <v>806</v>
-      </c>
-      <c r="C88" t="s">
-        <v>807</v>
-      </c>
-      <c r="E88" t="s">
-        <v>808</v>
-      </c>
       <c r="F88" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G88">
         <v>44901</v>
       </c>
       <c r="H88" s="49" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="I88" s="33">
         <v>4198860068</v>
       </c>
       <c r="J88" s="38" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
@@ -11220,84 +11088,84 @@
         <v>343</v>
       </c>
       <c r="B89" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="C89" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="E89" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="F89" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G89">
         <v>44446</v>
       </c>
       <c r="H89" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="I89" s="33" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="J89" s="38" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="43" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="B90" s="43" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C90" s="43" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="D90" s="43"/>
       <c r="E90" s="43" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="F90" s="43" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="G90" s="43">
         <v>46234</v>
       </c>
       <c r="H90" s="43" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="I90" s="45">
         <v>3176535361</v>
       </c>
       <c r="J90" s="44" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="B91" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="I91" s="33"/>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="B92" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C92" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="E92" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F92" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G92">
         <v>44105</v>
@@ -11306,19 +11174,19 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>826</v>
+      </c>
+      <c r="B93" t="s">
+        <v>827</v>
+      </c>
+      <c r="C93" t="s">
+        <v>828</v>
+      </c>
+      <c r="E93" t="s">
         <v>829</v>
       </c>
-      <c r="B93" t="s">
-        <v>830</v>
-      </c>
-      <c r="C93" t="s">
-        <v>831</v>
-      </c>
-      <c r="E93" t="s">
-        <v>832</v>
-      </c>
       <c r="F93" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G93">
         <v>44090</v>
@@ -11327,24 +11195,24 @@
         <v>4406476661</v>
       </c>
       <c r="J93" s="38" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="B94" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C94" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="E94" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="F94" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G94">
         <v>44094</v>
@@ -11353,19 +11221,19 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>833</v>
+      </c>
+      <c r="B95" t="s">
+        <v>834</v>
+      </c>
+      <c r="C95" t="s">
+        <v>835</v>
+      </c>
+      <c r="E95" t="s">
         <v>836</v>
       </c>
-      <c r="B95" t="s">
-        <v>837</v>
-      </c>
-      <c r="C95" t="s">
-        <v>838</v>
-      </c>
-      <c r="E95" t="s">
-        <v>839</v>
-      </c>
       <c r="F95" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G95">
         <v>44149</v>
@@ -11376,19 +11244,19 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="B96" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="C96" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="E96" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="F96" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G96">
         <v>44125</v>
@@ -11397,53 +11265,53 @@
         <v>2166421114</v>
       </c>
       <c r="J96" s="48" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="50" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="B97" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C97" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="E97" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F97" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G97">
         <v>44104</v>
       </c>
       <c r="H97" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="I97" s="33">
         <v>2164211203</v>
       </c>
       <c r="J97" s="38" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="43" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="B98" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="C98" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="E98" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F98" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G98">
         <v>44319</v>
@@ -11452,45 +11320,45 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>849</v>
+      </c>
+      <c r="B99" t="s">
+        <v>850</v>
+      </c>
+      <c r="C99" t="s">
+        <v>851</v>
+      </c>
+      <c r="E99" t="s">
         <v>852</v>
       </c>
-      <c r="B99" t="s">
-        <v>853</v>
-      </c>
-      <c r="C99" t="s">
-        <v>854</v>
-      </c>
-      <c r="E99" t="s">
-        <v>855</v>
-      </c>
       <c r="F99" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G99">
         <v>44128</v>
       </c>
       <c r="I99" s="33" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="J99" s="38" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>855</v>
+      </c>
+      <c r="B100" t="s">
+        <v>856</v>
+      </c>
+      <c r="C100" t="s">
+        <v>857</v>
+      </c>
+      <c r="E100" t="s">
         <v>858</v>
       </c>
-      <c r="B100" t="s">
-        <v>859</v>
-      </c>
-      <c r="C100" t="s">
-        <v>860</v>
-      </c>
-      <c r="E100" t="s">
-        <v>861</v>
-      </c>
       <c r="F100" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G100">
         <v>44128</v>
@@ -11499,53 +11367,53 @@
         <v>2166622235</v>
       </c>
       <c r="J100" s="38" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="B101" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="C101" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="E101" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F101" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G101">
         <v>44104</v>
       </c>
       <c r="H101" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="I101" s="33" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="J101" s="38" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>866</v>
+      </c>
+      <c r="B102" t="s">
+        <v>867</v>
+      </c>
+      <c r="C102" t="s">
+        <v>868</v>
+      </c>
+      <c r="E102" t="s">
         <v>869</v>
       </c>
-      <c r="B102" t="s">
-        <v>870</v>
-      </c>
-      <c r="C102" t="s">
-        <v>871</v>
-      </c>
-      <c r="E102" t="s">
-        <v>872</v>
-      </c>
       <c r="F102" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G102">
         <v>43452</v>
@@ -11554,31 +11422,31 @@
         <v>4402485552</v>
       </c>
       <c r="J102" s="38" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="34" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="B103" s="34" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="C103" s="34" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="D103" s="34"/>
       <c r="E103" s="34" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F103" s="34" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G103" s="34">
         <v>44114</v>
       </c>
       <c r="H103" s="34" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="I103" s="35">
         <v>2167712233</v>
@@ -11587,42 +11455,42 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="B104" t="s">
         <v>311</v>
       </c>
       <c r="C104" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="D104" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="E104" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="F104" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G104">
         <v>44233</v>
       </c>
       <c r="H104" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="I104" s="33" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="J104" s="38" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="34" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="B105" s="34" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="C105" s="34"/>
       <c r="D105" s="34"/>
@@ -11635,22 +11503,22 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>884</v>
+      </c>
+      <c r="B106" t="s">
+        <v>885</v>
+      </c>
+      <c r="C106" t="s">
+        <v>886</v>
+      </c>
+      <c r="D106" t="s">
         <v>887</v>
       </c>
-      <c r="B106" t="s">
-        <v>888</v>
-      </c>
-      <c r="C106" t="s">
-        <v>889</v>
-      </c>
-      <c r="D106" t="s">
-        <v>890</v>
-      </c>
       <c r="E106" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F106" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G106">
         <v>44104</v>
@@ -11659,24 +11527,24 @@
         <v>2163911444</v>
       </c>
       <c r="J106" s="38" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="B107" s="49" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="C107" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="E107" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F107" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G107">
         <v>44125</v>
@@ -11687,19 +11555,19 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="B108" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="C108" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="E108" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="F108" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G108">
         <v>44060</v>
@@ -11708,102 +11576,102 @@
         <v>4406029750</v>
       </c>
       <c r="J108" s="38" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="B109" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="C109" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="E109" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F109" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G109">
         <v>44131</v>
       </c>
       <c r="H109" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="I109" s="33" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="B110" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="C110" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="E110" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="F110" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G110">
         <v>44506</v>
       </c>
       <c r="H110" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="I110" s="33">
         <v>3307500333</v>
       </c>
       <c r="J110" s="38" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>906</v>
+      </c>
+      <c r="B111" t="s">
+        <v>907</v>
+      </c>
+      <c r="C111" t="s">
+        <v>908</v>
+      </c>
+      <c r="E111" t="s">
         <v>909</v>
       </c>
-      <c r="B111" t="s">
-        <v>910</v>
-      </c>
-      <c r="C111" t="s">
-        <v>911</v>
-      </c>
-      <c r="E111" t="s">
-        <v>912</v>
-      </c>
       <c r="F111" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G111">
         <v>44092</v>
       </c>
       <c r="I111" s="33" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="B112" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="C112" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="E112" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F112" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G112">
         <v>44125</v>
@@ -11814,25 +11682,25 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="B113" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="C113" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="E113" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F113" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G113">
         <v>44133</v>
       </c>
       <c r="H113" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="I113" s="33">
         <v>4402378070</v>
@@ -11841,80 +11709,80 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>918</v>
+      </c>
+      <c r="B114" t="s">
+        <v>919</v>
+      </c>
+      <c r="C114" t="s">
+        <v>920</v>
+      </c>
+      <c r="E114" t="s">
         <v>921</v>
       </c>
-      <c r="B114" t="s">
-        <v>922</v>
-      </c>
-      <c r="C114" t="s">
-        <v>923</v>
-      </c>
-      <c r="E114" t="s">
-        <v>924</v>
-      </c>
       <c r="F114" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G114">
         <v>44122</v>
       </c>
       <c r="H114" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="I114" s="33" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="J114" s="51" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B115" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="C115" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="E115" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="F115" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G115">
         <v>44021</v>
       </c>
       <c r="H115" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="I115" s="33" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="J115" s="38" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>931</v>
+      </c>
+      <c r="B116" t="s">
+        <v>932</v>
+      </c>
+      <c r="C116" t="s">
+        <v>933</v>
+      </c>
+      <c r="D116" t="s">
         <v>934</v>
       </c>
-      <c r="B116" t="s">
+      <c r="E116" t="s">
         <v>935</v>
       </c>
-      <c r="C116" t="s">
-        <v>936</v>
-      </c>
-      <c r="D116" t="s">
-        <v>937</v>
-      </c>
-      <c r="E116" t="s">
-        <v>938</v>
-      </c>
       <c r="F116" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G116">
         <v>44274</v>
@@ -11923,24 +11791,24 @@
         <v>3302392800</v>
       </c>
       <c r="J116" s="38" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>937</v>
+      </c>
+      <c r="B117" t="s">
+        <v>938</v>
+      </c>
+      <c r="C117" t="s">
+        <v>939</v>
+      </c>
+      <c r="E117" t="s">
         <v>940</v>
       </c>
-      <c r="B117" t="s">
-        <v>941</v>
-      </c>
-      <c r="C117" t="s">
-        <v>942</v>
-      </c>
-      <c r="E117" t="s">
-        <v>943</v>
-      </c>
       <c r="F117" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G117">
         <v>44070</v>
@@ -11949,53 +11817,53 @@
         <v>4407164900</v>
       </c>
       <c r="J117" s="38" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="B118" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="C118" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="E118" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F118" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G118">
         <v>44119</v>
       </c>
       <c r="H118" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="I118" s="33">
         <v>2164819548</v>
       </c>
       <c r="J118" s="38" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>947</v>
+      </c>
+      <c r="B119" t="s">
+        <v>948</v>
+      </c>
+      <c r="C119" t="s">
+        <v>949</v>
+      </c>
+      <c r="E119" t="s">
         <v>950</v>
       </c>
-      <c r="B119" t="s">
+      <c r="F119" t="s">
         <v>951</v>
-      </c>
-      <c r="C119" t="s">
-        <v>952</v>
-      </c>
-      <c r="E119" t="s">
-        <v>953</v>
-      </c>
-      <c r="F119" t="s">
-        <v>954</v>
       </c>
       <c r="G119">
         <v>30650</v>
@@ -12006,19 +11874,19 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>952</v>
+      </c>
+      <c r="B120" t="s">
+        <v>953</v>
+      </c>
+      <c r="C120" t="s">
+        <v>954</v>
+      </c>
+      <c r="E120" t="s">
         <v>955</v>
       </c>
-      <c r="B120" t="s">
-        <v>956</v>
-      </c>
-      <c r="C120" t="s">
-        <v>957</v>
-      </c>
-      <c r="E120" t="s">
-        <v>958</v>
-      </c>
       <c r="F120" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G120">
         <v>44436</v>
@@ -12029,22 +11897,22 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>956</v>
+      </c>
+      <c r="B121" t="s">
+        <v>957</v>
+      </c>
+      <c r="C121" t="s">
+        <v>958</v>
+      </c>
+      <c r="D121" t="s">
         <v>959</v>
       </c>
-      <c r="B121" t="s">
+      <c r="E121" t="s">
         <v>960</v>
       </c>
-      <c r="C121" t="s">
-        <v>961</v>
-      </c>
-      <c r="D121" t="s">
-        <v>962</v>
-      </c>
-      <c r="E121" t="s">
-        <v>963</v>
-      </c>
       <c r="F121" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G121">
         <v>43076</v>
@@ -12056,19 +11924,19 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="B122" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="C122" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="E122" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="F122" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G122">
         <v>44141</v>
@@ -12077,115 +11945,115 @@
         <v>9372766666</v>
       </c>
       <c r="J122" s="38" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>965</v>
+      </c>
+      <c r="B123" t="s">
+        <v>966</v>
+      </c>
+      <c r="C123" t="s">
+        <v>967</v>
+      </c>
+      <c r="E123" t="s">
         <v>968</v>
       </c>
-      <c r="B123" t="s">
-        <v>969</v>
-      </c>
-      <c r="C123" t="s">
-        <v>970</v>
-      </c>
-      <c r="E123" t="s">
-        <v>971</v>
-      </c>
       <c r="F123" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G123">
         <v>44004</v>
       </c>
       <c r="H123" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="I123" s="33">
         <v>4407487483</v>
       </c>
       <c r="J123" s="38" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>971</v>
+      </c>
+      <c r="B124" t="s">
+        <v>972</v>
+      </c>
+      <c r="C124" t="s">
+        <v>973</v>
+      </c>
+      <c r="E124" t="s">
         <v>974</v>
       </c>
-      <c r="B124" t="s">
-        <v>975</v>
-      </c>
-      <c r="C124" t="s">
-        <v>976</v>
-      </c>
-      <c r="E124" t="s">
-        <v>977</v>
-      </c>
       <c r="F124" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G124">
         <v>44143</v>
       </c>
       <c r="H124" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="I124" s="33" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="J124" s="38" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="34" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="B125" s="34" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="C125" s="34" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="D125" s="40"/>
       <c r="E125" s="34" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="F125" s="34" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G125" s="34">
         <v>44023</v>
       </c>
       <c r="H125" s="34" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="I125" s="35">
         <v>4405915393</v>
       </c>
       <c r="J125" s="41" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>983</v>
+      </c>
+      <c r="B126" t="s">
+        <v>984</v>
+      </c>
+      <c r="C126" t="s">
+        <v>985</v>
+      </c>
+      <c r="D126" t="s">
         <v>986</v>
       </c>
-      <c r="B126" t="s">
+      <c r="E126" t="s">
         <v>987</v>
       </c>
-      <c r="C126" t="s">
-        <v>988</v>
-      </c>
-      <c r="D126" t="s">
-        <v>989</v>
-      </c>
-      <c r="E126" t="s">
-        <v>990</v>
-      </c>
       <c r="F126" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G126">
         <v>44133</v>
@@ -12196,48 +12064,48 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>988</v>
+      </c>
+      <c r="B127" t="s">
+        <v>989</v>
+      </c>
+      <c r="C127" t="s">
+        <v>990</v>
+      </c>
+      <c r="E127" t="s">
         <v>991</v>
       </c>
-      <c r="B127" t="s">
-        <v>992</v>
-      </c>
-      <c r="C127" t="s">
-        <v>993</v>
-      </c>
-      <c r="E127" t="s">
-        <v>994</v>
-      </c>
       <c r="F127" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G127">
         <v>44470</v>
       </c>
       <c r="H127" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="I127" s="33" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="J127" s="38" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>995</v>
+      </c>
+      <c r="B128" t="s">
+        <v>996</v>
+      </c>
+      <c r="C128" t="s">
+        <v>997</v>
+      </c>
+      <c r="E128" t="s">
         <v>998</v>
       </c>
-      <c r="B128" t="s">
-        <v>999</v>
-      </c>
-      <c r="C128" t="s">
-        <v>1000</v>
-      </c>
-      <c r="E128" t="s">
-        <v>1001</v>
-      </c>
       <c r="F128" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G128">
         <v>44622</v>
@@ -12248,80 +12116,80 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>999</v>
+      </c>
+      <c r="B129" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C129" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E129" t="s">
         <v>1002</v>
       </c>
-      <c r="B129" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C129" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E129" t="s">
-        <v>1005</v>
-      </c>
       <c r="F129" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G129">
         <v>44312</v>
       </c>
       <c r="H129" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="I129" s="33">
         <v>3306451544</v>
       </c>
       <c r="J129" s="38" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B130" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C130" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D130" t="s">
         <v>1008</v>
       </c>
-      <c r="B130" t="s">
+      <c r="E130" t="s">
         <v>1009</v>
       </c>
-      <c r="C130" t="s">
-        <v>1010</v>
-      </c>
-      <c r="D130" t="s">
-        <v>1011</v>
-      </c>
-      <c r="E130" t="s">
-        <v>1012</v>
-      </c>
       <c r="F130" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G130">
         <v>44087</v>
       </c>
       <c r="H130" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="I130" s="33" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="J130" s="38" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="B131" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="C131" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="E131" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="F131" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G131">
         <v>44131</v>
@@ -12330,19 +12198,19 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B132" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C132" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E132" t="s">
         <v>1019</v>
       </c>
-      <c r="B132" t="s">
-        <v>1020</v>
-      </c>
-      <c r="C132" t="s">
-        <v>1021</v>
-      </c>
-      <c r="E132" t="s">
-        <v>1022</v>
-      </c>
       <c r="F132" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G132">
         <v>44092</v>
@@ -12353,19 +12221,19 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="B133" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="C133" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="E133" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="F133" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G133">
         <v>44125</v>
@@ -12376,19 +12244,19 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="B134" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="C134" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="E134" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="F134" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G134">
         <v>44060</v>
@@ -12399,50 +12267,50 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="43" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="B135" s="43" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="C135" s="43" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="D135" s="43"/>
       <c r="E135" s="43" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="F135" s="43" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G135" s="43">
         <v>44024</v>
       </c>
       <c r="H135" s="43" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="I135" s="45" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="J135" s="44" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="34" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="B136" s="34" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="C136" s="34" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="D136" s="34"/>
       <c r="E136" s="34" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="F136" s="34" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G136" s="34">
         <v>44023</v>
@@ -12452,25 +12320,25 @@
         <v>2164694602</v>
       </c>
       <c r="J136" s="36" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="43" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="B137" s="43" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C137" s="43" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="D137" s="43"/>
       <c r="E137" s="43" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="F137" s="43" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G137" s="43">
         <v>44092</v>
@@ -12480,15 +12348,15 @@
         <v>4405851439</v>
       </c>
       <c r="J137" s="44" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="34" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="B138" s="34" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="C138" s="34"/>
       <c r="D138" s="34"/>
@@ -12501,10 +12369,10 @@
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" s="40" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="B139" s="40" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="C139" s="40"/>
       <c r="D139" s="40"/>
@@ -12517,20 +12385,20 @@
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="43" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="B140" s="43" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="C140" s="43" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="D140" s="43"/>
       <c r="E140" s="43" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F140" s="43" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G140" s="43">
         <v>44121</v>
@@ -12540,82 +12408,82 @@
         <v>2163818100</v>
       </c>
       <c r="J140" s="44" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="B141" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="C141" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="E141" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F141" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G141">
         <v>44134</v>
       </c>
       <c r="H141" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="I141" s="33" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="J141" s="38" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B142" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C142" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E142" t="s">
         <v>1058</v>
       </c>
-      <c r="B142" t="s">
-        <v>1059</v>
-      </c>
-      <c r="C142" t="s">
-        <v>1060</v>
-      </c>
-      <c r="E142" t="s">
-        <v>1061</v>
-      </c>
       <c r="F142" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G142">
         <v>44710</v>
       </c>
       <c r="H142" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="I142" s="33" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="J142" s="38" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="B143" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="C143" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="E143" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="F143" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G143">
         <v>44224</v>
@@ -12626,19 +12494,19 @@
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B144" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C144" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E144" t="s">
         <v>1068</v>
       </c>
-      <c r="B144" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C144" t="s">
-        <v>1070</v>
-      </c>
-      <c r="E144" t="s">
-        <v>1071</v>
-      </c>
       <c r="F144" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G144">
         <v>44056</v>
@@ -12647,26 +12515,26 @@
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="43" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="B145" s="43" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="C145" s="43" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="D145" s="43"/>
       <c r="E145" s="43" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="F145" s="43" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G145" s="43">
         <v>44131</v>
       </c>
       <c r="H145" s="43" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="I145" s="45">
         <v>0</v>
@@ -12675,39 +12543,39 @@
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B146" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C146" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E146" t="s">
         <v>1076</v>
       </c>
-      <c r="B146" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C146" t="s">
-        <v>1078</v>
-      </c>
-      <c r="E146" t="s">
-        <v>1079</v>
-      </c>
       <c r="F146" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G146">
         <v>44618</v>
       </c>
       <c r="H146" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="I146" s="33" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="J146" s="38" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="34" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="B147" s="34" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="C147" s="34"/>
       <c r="D147" s="34"/>
@@ -12720,10 +12588,10 @@
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="34" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="B148" s="34" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="C148" s="34"/>
       <c r="D148" s="34"/>
